--- a/docs/xlsx/jobs-2026-08-28.xlsx
+++ b/docs/xlsx/jobs-2026-08-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="755">
   <si>
     <t>Title</t>
   </si>
@@ -430,6 +430,27 @@
     <t>https://www.conservationjobboard.com/job-listing-wildlife-program-manager-milwaukee-wisconsin/7120563019</t>
   </si>
   <si>
+    <t>Account Director (Direct Marketing, Non-Profit Fundraising)</t>
+  </si>
+  <si>
+    <t>The Avalon Consulting Group, LLC</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/05240d82db9840468615b5fd81db40b8-account-director-direct-marketing-non-profit-fundraising-the-avalon-consulting-group-llc-new-york</t>
+  </si>
+  <si>
     <t>Accounting Coordinator</t>
   </si>
   <si>
@@ -439,9 +460,6 @@
     <t>Bethesda, MD</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 27.88 - 29.81/hour</t>
   </si>
   <si>
@@ -451,6 +469,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/0b5c169f375447098de571044a09272f-accounting-coordinator-the-childrens-inn-at-the-national-institutes-of-health-bethesda</t>
   </si>
   <si>
+    <t>Actionable Data Lead</t>
+  </si>
+  <si>
+    <t>Baltimore's Promise</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 84000.00 - 84000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8eaf07f957194735a1609ddc690cfb6d-actionable-data-lead-baltimores-promise-baltimore</t>
+  </si>
+  <si>
     <t>Springwell, Inc.</t>
   </si>
   <si>
@@ -466,6 +502,75 @@
     <t>https://www.idealist.org/en/nonprofit-job/29ea5c4273604a05ae71baa1ab1568c3-administrative-assistant-springwell-inc-waltham</t>
   </si>
   <si>
+    <t>Administrative Assistant, Climate Change &amp; Environmental Justice</t>
+  </si>
+  <si>
+    <t>Lawyers for Good Government</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6e3c7c6f51044c782b1b73251040cdf-administrative-assistant-climate-change-environmental-justice-lawyers-for-good-government-washington</t>
+  </si>
+  <si>
+    <t>Adoption Home Study Support Specialist</t>
+  </si>
+  <si>
+    <t>The Cradle</t>
+  </si>
+  <si>
+    <t>Evanston, Illinois</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/55ceb0422fb140c7a10fc89074969d8b-adoption-home-study-support-specialist-the-cradle-evanston</t>
+  </si>
+  <si>
+    <t>Advocacy Coordinator</t>
+  </si>
+  <si>
+    <t>Waterkeeper Alliance</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/000b930349ee46dca35d4a3bb92ee3b8-advocacy-coordinator-waterkeeper-alliance-new-york</t>
+  </si>
+  <si>
+    <t>Affirmative Housing Attorney</t>
+  </si>
+  <si>
+    <t>Open Door Legal</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 83500.00 - 99500.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c3ee1a3d5bae41e9a1543966d9975201-affirmative-housing-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
     <t>AMS Administrator/Systems &amp; IT Technician</t>
   </si>
   <si>
@@ -478,12 +583,27 @@
     <t>USD 80000.00 - 98062.00/year</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/bb849f432c364a5b8c90d31b602a151d-ams-administratorsystems-it-technician-international-city-and-county-management-association-icma-washington</t>
   </si>
   <si>
+    <t>Asistente del Coordinador/a General (HOM)</t>
+  </si>
+  <si>
+    <t>Médicos Sin Fronteras en México AC</t>
+  </si>
+  <si>
+    <t>Ciudad de México, Ciudad de México, MX</t>
+  </si>
+  <si>
+    <t>MXN 28500.00 - 28500.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fef3229073814d239f2b526d6622548d-asistente-del-coordinadora-general-hom-medicos-sin-fronteras-en-mexico-ac-ciudad-de-mexico</t>
+  </si>
+  <si>
     <t>Asociación Conciencia busca Responsable de Programa Acompañando tu Futuro</t>
   </si>
   <si>
@@ -508,6 +628,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/2839a5b3eda343dbb7ea7c0e0623321f-asociacion-conciencia-busca-responsable-de-programa-acompanando-tu-futuro-asociacion-conciencia-neuquen</t>
   </si>
   <si>
+    <t>Assistant Director - Anti-Trafficking Services</t>
+  </si>
+  <si>
+    <t>Preble Street</t>
+  </si>
+  <si>
+    <t>Portland, Maine</t>
+  </si>
+  <si>
+    <t>USD 71000.00 - 71000.00/year</t>
+  </si>
+  <si>
+    <t>Sexual Abuse Human Trafficking, Children Youth, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6af2e0b1c374f96aa90ebe23d6a4c41-assistant-director-anti-trafficking-services-preble-street-portland</t>
+  </si>
+  <si>
+    <t>Assistant Director for Diversity, Equity and Inclusion</t>
+  </si>
+  <si>
+    <t>Southern New England Conference, United Church of Christ</t>
+  </si>
+  <si>
+    <t>Framingham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 71400.00 - 71400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce637defd00b46eb935003f8b0f38586-assistant-director-for-diversity-equity-and-inclusion-southern-new-england-conference-united-church-of-christ-framingham</t>
+  </si>
+  <si>
+    <t>Assistant to Program Leadership</t>
+  </si>
+  <si>
+    <t>Movement Voter Project</t>
+  </si>
+  <si>
+    <t>USD 76500.00 - 102000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d49c51f394464795aa89e309c1e4a94f-assistant-to-program-leadership-movement-voter-project-northampton</t>
+  </si>
+  <si>
+    <t>Assistant Vice President, Audience Engagement &amp; Growth</t>
+  </si>
+  <si>
+    <t>Charities Aid Foundation</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 138000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f11e062377e4715bd6546c4b6761033-assistant-vice-president-audience-engagement-growth-charities-aid-foundation-alexandria</t>
+  </si>
+  <si>
     <t>Assisted Living Ombudsman Program Manager</t>
   </si>
   <si>
@@ -535,6 +715,99 @@
     <t>https://www.idealist.org/en/business-job/54cacef5f9fd4da2aa0eab45c14e7112-associate-clinical-director-watch-hill-therapy-chicago</t>
   </si>
   <si>
+    <t>Associate Communications Manager</t>
+  </si>
+  <si>
+    <t>C&amp;O Canal Trust</t>
+  </si>
+  <si>
+    <t>Williamsport, Maryland</t>
+  </si>
+  <si>
+    <t>Economic Development, Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a455f997d6ed471883cb2dc8f24d3d6f-associate-communications-manager-co-canal-trust-williamsport</t>
+  </si>
+  <si>
+    <t>Associate Director, Donor Communications</t>
+  </si>
+  <si>
+    <t>ClimateWorks Foundation</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c92c951dc504d938416055359ff6cde-associate-director-donor-communications-climateworks-foundation-san-francisco</t>
+  </si>
+  <si>
+    <t>Associate Director, Law &amp; Policy Reform, Data for Health Program</t>
+  </si>
+  <si>
+    <t>Campaign for Tobacco-Free Kids/Global Health Advocacy Incubator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbc57f7ab24c44e8be8a34118ba10109-associate-director-law-policy-reform-data-for-health-program-campaign-for-tobacco-free-kidsglobal-health-advocacy-incubator-washington</t>
+  </si>
+  <si>
+    <t>Associate Organizer</t>
+  </si>
+  <si>
+    <t>Common Ground &amp; Tenants United</t>
+  </si>
+  <si>
+    <t>Milwaukee, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Economic Development, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/78f95f77d98542b6a64736ecebba8ad3-associate-organizer-common-ground-tenants-united-milwaukee</t>
+  </si>
+  <si>
+    <t>Bilingual Licensed Mental Health Counselor</t>
+  </si>
+  <si>
+    <t>Center for Independence of the Disabled, NY</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/70f520ddff21494ca40366f56f53da05-bilingual-licensed-mental-health-counselor-center-for-independence-of-the-disabled-ny-new-york</t>
+  </si>
+  <si>
+    <t>Bilingual Permanency Social Worker – Part-Time</t>
+  </si>
+  <si>
+    <t>Family Builders by Adoption</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 51129.00 - 51129.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a0e890ebce1249d18e9270c2eadd02d3-bilingual-permanency-social-worker-part-time-family-builders-by-adoption-san-francisco</t>
+  </si>
+  <si>
     <t>Billing Specialist</t>
   </si>
   <si>
@@ -550,15 +823,9 @@
     <t>Partners for Andean Community Health</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>Contract</t>
   </si>
   <si>
-    <t>Health Medicine</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/c78109688acb4f50b976b1ecf23d97cd-bookkeeperaccountant-partners-for-andean-community-health-west-hartford</t>
   </si>
   <si>
@@ -577,15 +844,123 @@
     <t>https://www.idealist.org/en/nonprofit-job/24bfbdba233e4475a12dda78da270684-business-immigration-associate-coefficient-giving-san-francisco</t>
   </si>
   <si>
+    <t>Campaign Counsel</t>
+  </si>
+  <si>
+    <t>Government Accountability Project</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Job Workplace, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c18a8a5ea3a49e3bd0377d523ad6cfc-campaign-counsel-government-accountability-project-washington</t>
+  </si>
+  <si>
+    <t>Campaign Director</t>
+  </si>
+  <si>
+    <t>Sierra Club</t>
+  </si>
+  <si>
+    <t>USD 210000.00 - 220000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/76043735677b4db8b83ba7c9fc56a1cf-campaign-director-sierra-club-oakland</t>
+  </si>
+  <si>
+    <t>Captadores/as de Fondos en vía pública para Ingeniería Sin Fronteras Argentina -CABA - Turno Mañana</t>
+  </si>
+  <si>
+    <t>Ingeniería Sin Fronteras Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/92196ac559be44e9bd1c99b3b897df29-captadoresas-de-fondos-en-via-publica-para-ingenieria-sin-fronteras-argentina-caba-turno-manana-ingenieria-sin-fronteras-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Captadores/as de Fondos en vía pública para Ingeniería Sin Fronteras Argentina Turno Tarde</t>
+  </si>
+  <si>
+    <t>Community Development, Science Technology, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d1d353cd5cd42f3b2aa3262c9dc345e-captadoresas-de-fondos-en-via-publica-para-ingenieria-sin-fronteras-argentina-turno-tarde-ingenieria-sin-fronteras-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Disability Rights New Mexico</t>
+  </si>
+  <si>
+    <t>Albuquerque, New Mexico</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1686d83c304f43f2a19d11c796147f2e-chief-executive-officer-disability-rights-new-mexico-albuquerque</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>Climate Interactive</t>
+  </si>
+  <si>
+    <t>USD 155000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9154b4fd7e4b44fb8d66c75707073cab-chief-operating-officer-climate-interactive-washington</t>
+  </si>
+  <si>
+    <t>CMS Program Associate</t>
+  </si>
+  <si>
+    <t>Brooklyn Conservatory of Music</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e87c9acca95f4210bc42c09975d6d17f-cms-program-associate-brooklyn-conservatory-of-music-kings-county</t>
+  </si>
+  <si>
+    <t>College Advisor</t>
+  </si>
+  <si>
+    <t>ScholarMatch</t>
+  </si>
+  <si>
+    <t>Remote (San Francisco, CA)</t>
+  </si>
+  <si>
+    <t>USD 24.04 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/151a6363a28348659a003d3a12b53b97-college-advisor-scholarmatch-san-francisco</t>
+  </si>
+  <si>
     <t>Community &amp; Events Associate</t>
   </si>
   <si>
     <t>Collider</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 60000.00 - 80000.00/year</t>
   </si>
   <si>
@@ -595,6 +970,75 @@
     <t>https://www.idealist.org/en/job/4f394f12b72d499282eea71a6223dda2-community-events-associate-collider-new-york</t>
   </si>
   <si>
+    <t>Community Engagement &amp; Partnership Specialist</t>
+  </si>
+  <si>
+    <t>Echoes of Hope</t>
+  </si>
+  <si>
+    <t>El Segundo, California</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0cf35d3b347f42ddad61f76af06aaa30-community-engagement-partnership-specialist-echoes-of-hope-el-segundo</t>
+  </si>
+  <si>
+    <t>Consultor comercial e MKT de moda</t>
+  </si>
+  <si>
+    <t>Instituto Ecotece</t>
+  </si>
+  <si>
+    <t>São Paulo, São Paulo, BR</t>
+  </si>
+  <si>
+    <t>BRL 3000.00 - 4000.00/month</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5af17dcc5c764874a39a33d66673ae41-consultor-comercial-e-mkt-de-moda-instituto-ecotece-sao-paulo</t>
+  </si>
+  <si>
+    <t>Content Senior Manager</t>
+  </si>
+  <si>
+    <t>Washington Conservation Action</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7743630edb374376947f94e34a31e620-content-senior-manager-washington-conservation-action-seattle</t>
+  </si>
+  <si>
+    <t>Coordinator, Monitoring, Evaluation, &amp; Learning (MEL)</t>
+  </si>
+  <si>
+    <t>Episcopal Relief &amp; Development</t>
+  </si>
+  <si>
+    <t>USD 34.00 - 36.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed29fca6fd954db8b45053182eca995e-coordinator-monitoring-evaluation-learning-mel-episcopal-relief-development-new-york</t>
+  </si>
+  <si>
     <t>Counsel (Voting Rights Project)</t>
   </si>
   <si>
@@ -610,6 +1054,120 @@
     <t>https://www.idealist.org/en/nonprofit-job/31c7045b32294ded83958e664295fb2a-counsel-voting-rights-project-fair-elections-center-washington</t>
   </si>
   <si>
+    <t>Counseling Manager</t>
+  </si>
+  <si>
+    <t>Ability Now Bay Area</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa7f4b5e279a4e81a88a23fd5f277155-counseling-manager-ability-now-bay-area-oakland</t>
+  </si>
+  <si>
+    <t>Dependency Staff Attorney</t>
+  </si>
+  <si>
+    <t>Legal Services for Children</t>
+  </si>
+  <si>
+    <t>USD 80474.00 - 97357.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d67bfb204b874f26ac5431ad717cd5ad-dependency-staff-attorney-legal-services-for-children-san-francisco</t>
+  </si>
+  <si>
+    <t>Deputy Chief, Advancement</t>
+  </si>
+  <si>
+    <t>Church World Service New York</t>
+  </si>
+  <si>
+    <t>USD 128800.00 - 161000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Disaster Relief, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a0c1f7de37f47df898a886eb7ac78e9-deputy-chief-advancement-church-world-service-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Deputy Country Director</t>
+  </si>
+  <si>
+    <t>Cure Blindness Project</t>
+  </si>
+  <si>
+    <t>Remote (ET)</t>
+  </si>
+  <si>
+    <t>USD 37500.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/33b20310614d4aca9d80508ddffd444d-deputy-country-director-cure-blindness-project-addis-ababa</t>
+  </si>
+  <si>
+    <t>Development &amp; Membership Manager</t>
+  </si>
+  <si>
+    <t>The Ruth Bancroft Garden</t>
+  </si>
+  <si>
+    <t>Walnut Creek, California</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 76000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e61617698f73464fac629ec1cabbe6da-development-membership-manager-the-ruth-bancroft-garden-walnut-creek</t>
+  </si>
+  <si>
+    <t>Development Assistant - Part-time</t>
+  </si>
+  <si>
+    <t>The Center for Empowerment and Education</t>
+  </si>
+  <si>
+    <t>Danbury, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f36bd31a481841f79bb9f287a76c6d41-development-assistant-part-time-the-center-for-empowerment-and-education-danbury</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>InnerCity Struggle</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 31.00 - 33.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/443df267131242b480621dc56520b1b3-development-associate-innercity-struggle-los-angeles</t>
+  </si>
+  <si>
     <t>Development Manager</t>
   </si>
   <si>
@@ -625,6 +1183,198 @@
     <t>https://www.idealist.org/en/job/65bede3702fe48deb9e897f9919780aa-development-manager-all-stars-project-inc-newark</t>
   </si>
   <si>
+    <t>Development Relations Lead, Interdisciplinary and Engaged Science</t>
+  </si>
+  <si>
+    <t>Aspen Global Change Institute</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/59766347af92405bbf415d1093231f6a-development-relations-lead-interdisciplinary-and-engaged-science-aspen-global-change-institute-basalt</t>
+  </si>
+  <si>
+    <t>Director of Agriculture</t>
+  </si>
+  <si>
+    <t>Cityseed</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Entrepreneurship, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1fbd90650ebb46b396fa91ac4e881d84-director-of-agriculture-cityseed-new-haven</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Habitat for Humanity Portland Region</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 80705.00 - 121057.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Philanthropy, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1c3801fc9d63460ca81d895e25c7bf50-director-of-development-habitat-for-humanity-portland-region-portland</t>
+  </si>
+  <si>
+    <t>Town Hall Seattle</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbff017190df43c096b39f874344c007-director-of-development-town-hall-seattle-seattle</t>
+  </si>
+  <si>
+    <t>Director of Foundation Relations</t>
+  </si>
+  <si>
+    <t>Southern Environmental Law Center</t>
+  </si>
+  <si>
+    <t>Charlottesville, Virginia</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 177900.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d86c1fea2bf149e5bb7bdf971567e89f-director-of-foundation-relations-southern-environmental-law-center-charlottesville</t>
+  </si>
+  <si>
+    <t>Director of Marketing &amp; Creative</t>
+  </si>
+  <si>
+    <t>Save the Redwoods League</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b970cc5761274e76b658d0332640f28e-director-of-marketing-creative-save-the-redwoods-league-san-francisco</t>
+  </si>
+  <si>
+    <t>Director of Policy and Legislative Affairs</t>
+  </si>
+  <si>
+    <t>California CASA Association</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Legal Assistance, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7b5c3346a0940469bf9abfb316658f4-director-of-policy-and-legislative-affairs-california-casa-association-sacramento</t>
+  </si>
+  <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>Open Doors for Refugees</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Volunteering, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8a386594f4c94ff69307ebe320f69dd8-director-of-programs-open-doors-for-refugees-madison</t>
+  </si>
+  <si>
+    <t>Director, State Advocacy</t>
+  </si>
+  <si>
+    <t>Parent Project Muscular Dystrophy</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5faff48d2e71449cbe2dac2a89a7de57-director-state-advocacy-parent-project-muscular-dystrophy-washington</t>
+  </si>
+  <si>
+    <t>Education Lead Organizer</t>
+  </si>
+  <si>
+    <t>ACTION Council of Monterey County</t>
+  </si>
+  <si>
+    <t>Salinas, California</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 76285.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d32d3d9b105f4e53aa206f6c1de19a36-education-lead-organizer-action-council-of-monterey-county-salinas</t>
+  </si>
+  <si>
+    <t>Employment Resource Navigator</t>
+  </si>
+  <si>
+    <t>Mandela Partners</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cb1c7cf5f72c43bcaa3538ad702c7f8d-employment-resource-navigator-mandela-partners-oakland</t>
+  </si>
+  <si>
+    <t>Engineering Team Lead- Remote</t>
+  </si>
+  <si>
+    <t>Chapter One NFP</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/628689630a354a529bee87a1432c8a70-engineering-team-lead-remote-chapter-one-nfp-odessa</t>
+  </si>
+  <si>
     <t>Executive Assistant and Governance Associate</t>
   </si>
   <si>
@@ -640,6 +1390,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/8a3530d3900c40eb976bc93f74f9ec1e-executive-assistant-and-governance-associate-edlavitch-dc-jewish-community-center-washington</t>
   </si>
   <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Rochester Area Neighborhood House</t>
+  </si>
+  <si>
+    <t>detroit metropolitan area, Michigan</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Poverty, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5d6991e3e0564f19869487e31cbaf57e-executive-director-rochester-area-neighborhood-house-detroit-metropolitan-area</t>
+  </si>
+  <si>
     <t>Executive Director (part-time)</t>
   </si>
   <si>
@@ -655,6 +1423,69 @@
     <t>https://www.idealist.org/en/nonprofit-job/4a10c85e8b8840bea49aff280e426dc3-executive-director-part-time-national-neutropenia-network-cincinnati</t>
   </si>
   <si>
+    <t>Executive Director of the Center for Talent Development</t>
+  </si>
+  <si>
+    <t>JCC Association</t>
+  </si>
+  <si>
+    <t>USD 320000.00 - 350000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2f7858b14764081b8b8cceb31566da5-executive-director-of-the-center-for-talent-development-jcc-association-new-york</t>
+  </si>
+  <si>
+    <t>Executive Office Coordinator</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba44f7eddd7349128ef7736fffa8fb26-executive-office-coordinator-jcc-association-new-york</t>
+  </si>
+  <si>
+    <t>Family Child Specialist - EHS - Children's Corner</t>
+  </si>
+  <si>
+    <t>University Settlement Society of New York</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 51000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b18045409b848beb3924a0c1f4a125a-family-child-specialist-ehs-childrens-corner-university-settlement-society-of-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Family Worker - EHS - Children's Corner</t>
+  </si>
+  <si>
+    <t>USD 44000.00 - 51000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/18e8dd23df8c4906a1911409174083a9-family-worker-ehs-childrens-corner-university-settlement-society-of-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Finance &amp; Administration Director</t>
+  </si>
+  <si>
+    <t>Audubon Society of Western Pennsylvania</t>
+  </si>
+  <si>
+    <t>Pittsburgh, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Education, Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ebceb69bbf5b4e439ffc5d59f98f72a9-finance-administration-director-audubon-society-of-western-pennsylvania-pittsburgh</t>
+  </si>
+  <si>
     <t>Finance and Operations Manager</t>
   </si>
   <si>
@@ -670,6 +1501,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/f38e070a444e430ba8bde487b2293321-finance-and-operations-manager-the-circulate-initiative-new-york</t>
   </si>
   <si>
+    <t>Foundation Relations Assistant</t>
+  </si>
+  <si>
+    <t>The Public Interest Network</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Consumer Protection, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/74af2fd7267d42fab39c02bc39a8dc45-foundation-relations-assistant-the-public-interest-network-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34303c922c2948f8b8065ece4fcc3e33-foundation-relations-assistant-the-public-interest-network-washington</t>
+  </si>
+  <si>
     <t>Freelancer season Fundraiser</t>
   </si>
   <si>
@@ -694,6 +1543,84 @@
     <t>https://www.idealist.org/en/nonprofit-job/b8d0eba516204b5f9419803402d5e1ad-geriatric-support-services-coordinator-springwell-inc-waltham</t>
   </si>
   <si>
+    <t>GESTOR/A DE FARMACIA DE LA MISIÓN</t>
+  </si>
+  <si>
+    <t>MXN 49500.00 - 49500.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c79de56cc57642139504dc587b3d55e4-gestora-de-farmacia-de-la-mision-medicos-sin-fronteras-en-mexico-ac-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>GLAD Law Assistant Director of Strategic Communications and Content</t>
+  </si>
+  <si>
+    <t>Positively Partners</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/2a81f500b9d34f7cbeeaf5ab91db04cc-glad-law-assistant-director-of-strategic-communications-and-content-positively-partners-boston</t>
+  </si>
+  <si>
+    <t>Grant Manager</t>
+  </si>
+  <si>
+    <t>RISE Academy</t>
+  </si>
+  <si>
+    <t>Omaha, NE</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/511b011f59f04d9b8f45f46efe4b1881-grant-manager-rise-academy-omaha</t>
+  </si>
+  <si>
+    <t>Grants Manager</t>
+  </si>
+  <si>
+    <t>Amah Mutsun Land Trust</t>
+  </si>
+  <si>
+    <t>Santa Cruz, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc9c3f4d156a4b08902572947cbb613a-grants-manager-amah-mutsun-land-trust-santa-cruz</t>
+  </si>
+  <si>
+    <t>Grants Specialist</t>
+  </si>
+  <si>
+    <t>Sisters of St Joseph Neighborhood Network</t>
+  </si>
+  <si>
+    <t>Erie, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae688bc031064dd080ae05caba39a7db-grants-specialist-sisters-of-st-joseph-neighborhood-network-erie</t>
+  </si>
+  <si>
+    <t>HBCI Crisis Interventionist</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/88cf371df6e1409b80b05cf762fd6bf0-hbci-crisis-interventionist-center-for-independence-of-the-disabled-ny-new-york</t>
+  </si>
+  <si>
     <t>Head of Finance</t>
   </si>
   <si>
@@ -709,6 +1636,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/4955921c78174350a9962141d8ebe627-head-of-finance-welthungerhilfe-damascus</t>
   </si>
   <si>
+    <t>High School Mentor</t>
+  </si>
+  <si>
+    <t>Summer Search</t>
+  </si>
+  <si>
+    <t>USD 62015.00 - 71484.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e686ec3ae1e74ab3882608293fba028c-high-school-mentor-summer-search-oakland</t>
+  </si>
+  <si>
+    <t>Human Resources and Finance Assistant</t>
+  </si>
+  <si>
+    <t>USD 28.13 - 31.11/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cd4a2eb200884c13adc407509cc10949-human-resources-and-finance-assistant-southern-environmental-law-center-charlottesville</t>
+  </si>
+  <si>
+    <t>Human Resources Generalist</t>
+  </si>
+  <si>
+    <t>amfAR</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/924788295a5649af87f57bf684e4fcd3-human-resources-generalist-amfar-new-york</t>
+  </si>
+  <si>
     <t>Information &amp; Referral Specialist</t>
   </si>
   <si>
@@ -730,9 +1696,6 @@
     <t>Alexandria, Virginia</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 22.00 - 25.00/hour</t>
   </si>
   <si>
@@ -742,6 +1705,84 @@
     <t>https://www.idealist.org/en/nonprofit-job/0b9c5c03ff0d41a789254ec7fed4c657-kitchen-coordinator-carpenters-shelter-alexandria</t>
   </si>
   <si>
+    <t>Legislative Advocate</t>
+  </si>
+  <si>
+    <t>U.S. PIRG</t>
+  </si>
+  <si>
+    <t>USD 41750.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Consumer Protection, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b64a876bd5c740cdafabdbd6442278af-legislative-advocate-us-pirg-washington</t>
+  </si>
+  <si>
+    <t>Legislative and Political Advocate</t>
+  </si>
+  <si>
+    <t>AFSCME Maryland</t>
+  </si>
+  <si>
+    <t>USD 60978.00 - 92235.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e0a85b06fc1f45c6b38c2854c88702eb-legislative-and-political-advocate-afscme-maryland-baltimore</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Membership Manager</t>
+  </si>
+  <si>
+    <t>Merola Opera Program</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7143c9254dee400eb959892571e1b57f-marketing-membership-manager-merola-opera-program-san-francisco</t>
+  </si>
+  <si>
+    <t>Marketing Coordinator</t>
+  </si>
+  <si>
+    <t>National Grants Management Association</t>
+  </si>
+  <si>
+    <t>Remote (Virginia)</t>
+  </si>
+  <si>
+    <t>Job Workplace, Philanthropy, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/14f46a5d35654eec9a46dc23f8083f42-marketing-coordinator-national-grants-management-association-sterling</t>
+  </si>
+  <si>
+    <t>Remote (Georgia)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/93ca3b8a28324c5b88e84dcadfb3b688-marketing-coordinator-national-grants-management-association-sterling</t>
+  </si>
+  <si>
+    <t>MEL &amp; Data Specialist</t>
+  </si>
+  <si>
+    <t>One Good Turn Global Health</t>
+  </si>
+  <si>
+    <t>USD 30000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/168b06b85ef6401481e67df6fe18135f-mel-data-specialist-one-good-turn-global-health-austin</t>
+  </si>
+  <si>
     <t>Membership Coordinator</t>
   </si>
   <si>
@@ -757,6 +1798,114 @@
     <t>https://www.idealist.org/en/job/3f93b88644584dc286addac5627436ea-membership-coordinator-national-organization-for-women-washington</t>
   </si>
   <si>
+    <t>New York Conservation Advocate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>USD 41750.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe42194bf0c8449792c108d6f65a3f51-new-york-conservation-advocate-environment-america-rochester</t>
+  </si>
+  <si>
+    <t>NY Connects Benefits Counselor - Bronx</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da1f0115aa044567aed876757cbb0980-ny-connects-benefits-counselor-bronx-center-for-independence-of-the-disabled-ny-bronx-county</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Center for Tech and Civic Life</t>
+  </si>
+  <si>
+    <t>USD 79770.51 - 86313.58/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f8aafd0689c41bbb0b3632796d296a0-operations-manager-center-for-tech-and-civic-life-chicago</t>
+  </si>
+  <si>
+    <t>Paralegal - Opportunity Under Law</t>
+  </si>
+  <si>
+    <t>Public Counsel</t>
+  </si>
+  <si>
+    <t>USD 60903.12 - 65030.88/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2b459bd54c9487cb685021668302433-paralegal-opportunity-under-law-public-counsel-los-angeles</t>
+  </si>
+  <si>
+    <t>Pathways Coordinator</t>
+  </si>
+  <si>
+    <t>ZUMIX, Inc.</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a2ba074ac8f446e4b99aa3395b2d032f-pathways-coordinator-zumix-inc-boston</t>
+  </si>
+  <si>
+    <t>Political Director</t>
+  </si>
+  <si>
+    <t>Service Employees International Union Local 105</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 103991.00 - 120327.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da7abd81d866402d92492cbfbc9db3b0-political-director-service-employees-international-union-local-105-denver</t>
+  </si>
+  <si>
+    <t>Prevention &amp; Outreach Specialist</t>
+  </si>
+  <si>
+    <t>Respect Together</t>
+  </si>
+  <si>
+    <t>Harrisburg, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55286.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/706f0f68e0004d07a8e6b12a2081ca3d-prevention-outreach-specialist-respect-together-harrisburg</t>
+  </si>
+  <si>
     <t>Principal Director, Program Development *Remote*</t>
   </si>
   <si>
@@ -781,15 +1930,33 @@
     <t>Aldeas Infantiles SOS Argentina</t>
   </si>
   <si>
-    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
-  </si>
-  <si>
-    <t>Children Youth, Family</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/c8498ae7ec1e49a3bdf3ea9c001df5f3-profesional-para-tareas-administrativas-aldeas-infantiles-sos-argentina-buenos-aires</t>
   </si>
   <si>
+    <t>Program Assistant</t>
+  </si>
+  <si>
+    <t>U.S. Dream Academy</t>
+  </si>
+  <si>
+    <t>USD 17.00 - 19.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8dfcb3deac25417d971efd82688966a4-program-assistant-us-dream-academy-baltimore</t>
+  </si>
+  <si>
+    <t>Program Associate, JWB Jewish Chaplains Council</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/adcfcfffea6e46108c7767196067844d-program-associate-jwb-jewish-chaplains-council-jcc-association-new-york</t>
+  </si>
+  <si>
     <t>Program Coordinator</t>
   </si>
   <si>
@@ -799,12 +1966,45 @@
     <t>USD 15.00 - 18.00/hour</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d416593b47ec4afeaf6ec09c9b6c2aa7-program-coordinator-lulac-national-educational-service-centers-inc-washington</t>
   </si>
   <si>
+    <t>USD 52000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1baecf5efe0f4ae1a88b20c161777a21-program-coordinator-us-dream-academy-baltimore</t>
+  </si>
+  <si>
+    <t>Program Director (PD-1)</t>
+  </si>
+  <si>
+    <t>Social Science Research Council</t>
+  </si>
+  <si>
+    <t>USD 145454.00 - 145454.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95366fc582bd45e9b8fa0c9c35a90900-program-director-pd-1-social-science-research-council-new-york</t>
+  </si>
+  <si>
+    <t>Program Manager - Language Justice Program</t>
+  </si>
+  <si>
+    <t>Masa</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Urban Areas, Immigrants Or Refugees, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8ec609f3e2a34fb3bb5de2978dcae5a5-program-manager-language-justice-program-masa-bronx</t>
+  </si>
+  <si>
     <t>Project Coordinator (Belize and Guatemala Travel Programs)</t>
   </si>
   <si>
@@ -817,9 +2017,6 @@
     <t>GTQ 300.00 - 700.00/day</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d32f9a457df147ceb1969855237b873a-project-coordinator-belize-and-guatemala-travel-programs-global-public-service-academies-quetzaltenango</t>
   </si>
   <si>
@@ -832,6 +2029,93 @@
     <t>https://www.idealist.org/en/nonprofit-job/9c8aa8b40a3644758cb01adbecc916b3-registered-nurse-rn-springwell-inc-waltham</t>
   </si>
   <si>
+    <t>Research &amp; Investigations Assistant</t>
+  </si>
+  <si>
+    <t>White Coat Waste Project</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/245aa76311674e17904a3ee49aac495e-research-investigations-assistant-white-coat-waste-project-washington</t>
+  </si>
+  <si>
+    <t>Retreat Program co-Manager (anticipated hire)</t>
+  </si>
+  <si>
+    <t>LoveYourBrain</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/98a3c180e05f4b2eacb6630c06fa7b9e-retreat-program-co-manager-anticipated-hire-loveyourbrain-norwich</t>
+  </si>
+  <si>
+    <t>SANE Coordinator</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 57876.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45ac74e6c0ee4548b1be588cc5a99bbb-sane-coordinator-respect-together-harrisburg</t>
+  </si>
+  <si>
+    <t>Senior Account Director (Direct Marketing, Non-Profit Fundraising)</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/84d2437722464ec5bf01ea5e52c8037e-senior-account-director-direct-marketing-non-profit-fundraising-the-avalon-consulting-group-llc-washington</t>
+  </si>
+  <si>
+    <t>Senior Associate, People &amp; Culture</t>
+  </si>
+  <si>
+    <t>Repair the World</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca50d827fe4e4d28aadfe433050d0b5a-senior-associate-people-culture-repair-the-world-new-york</t>
+  </si>
+  <si>
+    <t>Senior Data Analyst (SQL Expertise)</t>
+  </si>
+  <si>
+    <t>United Hospital Fund of New York</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3cfe301450c448b483fe220a5730ec65-senior-data-analyst-sql-expertise-united-hospital-fund-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Senior Digital Program Manager (Fully remote, Non-profit Fundraising)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/bfd99c1710704704bc7b00d9845732a2-senior-digital-program-manager-fully-remote-non-profit-fundraising-the-avalon-consulting-group-llc-annapolis</t>
+  </si>
+  <si>
     <t>Senior Director for Philanthropic Engagement</t>
   </si>
   <si>
@@ -844,6 +2128,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/19b8d0776d5a4216a13887a6ac05c8cf-senior-director-for-philanthropic-engagement-edlavitch-dc-jewish-community-center-washington</t>
   </si>
   <si>
+    <t>Senior Manager, Employer Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d1bfacc020544c9dbb42c9e3c90b0be3-senior-manager-employer-engagement-baltimores-promise-baltimore</t>
+  </si>
+  <si>
+    <t>Senior Program Associate, Bay Area</t>
+  </si>
+  <si>
+    <t>San Francisco Bay Area, California</t>
+  </si>
+  <si>
+    <t>USD 70500.00 - 72500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9cca13f2e081472391c0410a7e518566-senior-program-associate-bay-area-repair-the-world-san-francisco-bay-area</t>
+  </si>
+  <si>
+    <t>Sheva Center Communication, Technology, and Operations Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/06c34e6e875b4fee9c4475f0757bf62b-sheva-center-communication-technology-and-operations-associate-jcc-association-new-york</t>
+  </si>
+  <si>
+    <t>St. Johns Riverkeeper</t>
+  </si>
+  <si>
+    <t>ST JOHNS RIVERKEEPER INC</t>
+  </si>
+  <si>
+    <t>JACKSONVILLE, Florida</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f3989018d910419a91ac52f63156d8d2-st-johns-riverkeeper-st-johns-riverkeeper-inc-jacksonville</t>
+  </si>
+  <si>
     <t>Staff Attorney - Elder Law/General Practice - Poughkeepsie</t>
   </si>
   <si>
@@ -862,6 +2185,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/99df428667d34eb08ce62d0286d6185b-staff-attorney-elder-lawgeneral-practice-poughkeepsie-legal-services-of-the-hudson-valley-poughkeepsie</t>
   </si>
   <si>
+    <t>Staff Attorney - Immigrants' Rights (Anti-Detention Team)</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 103400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eb266e72beb7467db6762cca28ff742e-staff-attorney-immigrants-rights-anti-detention-team-public-counsel-los-angeles</t>
+  </si>
+  <si>
     <t>Teaching Artists - GENuine Connections®</t>
   </si>
   <si>
@@ -877,6 +2209,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/5760c9c4975048d3b3adde45ed11cb2b-teaching-artists-genuine-connections-dorot-new-york</t>
   </si>
   <si>
+    <t>Tech Lead — Backend &amp; Platform</t>
+  </si>
+  <si>
+    <t>Basta</t>
+  </si>
+  <si>
+    <t>USD 180000.00 - 220000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bda668d46c8441309c7ac08d0d7b920d-tech-lead-backend-platform-basta-new-york</t>
+  </si>
+  <si>
+    <t>Toxics Campaign Director</t>
+  </si>
+  <si>
+    <t>USD 42000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Policy, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c0f39c18f5fc415ab018922e6721a476-toxics-campaign-director-us-pirg-boston</t>
+  </si>
+  <si>
+    <t>Trail Engagement Manager</t>
+  </si>
+  <si>
+    <t>Lewis and Clark Trail Heritage Foundation</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Travel Hospitality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fecb2d1f15c843f3bf5b2a28735850bb-trail-engagement-manager-lewis-and-clark-trail-heritage-foundation-great-falls</t>
+  </si>
+  <si>
     <t>Undercover Investigator, Germany</t>
   </si>
   <si>
@@ -890,6 +2264,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/3af70c630cbd4f239c7142b40bb3afc3-undercover-investigator-germany-animal-equality-los-angeles</t>
+  </si>
+  <si>
+    <t>Vision Urbana Social Worker MSW</t>
+  </si>
+  <si>
+    <t>Vision Urbana, Inc.</t>
+  </si>
+  <si>
+    <t>USD 50000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Seniors Retirement, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7e87a79d42564b7b886a33496b54faca-vision-urbana-social-worker-msw-vision-urbana-inc-new-york</t>
   </si>
 </sst>
 </file>
@@ -1925,7 +3314,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -1989,53 +3378,53 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
         <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s">
         <v>141</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>157</v>
@@ -2044,10 +3433,10 @@
         <v>158</v>
       </c>
       <c r="D5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" t="s">
         <v>159</v>
-      </c>
-      <c r="E5" t="s">
-        <v>154</v>
       </c>
       <c r="F5" t="s">
         <v>160</v>
@@ -2058,646 +3447,2923 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="F6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
         <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F7" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s">
         <v>141</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F8" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
         <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F9" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="F10" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B11" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D11" t="s">
         <v>141</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="F11" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="E12" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="F12" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B13" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="E13" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
       <c r="F13" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B14" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C14" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D14" t="s">
         <v>141</v>
       </c>
       <c r="E14" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F14" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C15" t="s">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="D15" t="s">
         <v>141</v>
       </c>
       <c r="E15" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F15" t="s">
-        <v>206</v>
+        <v>143</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B16" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C16" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="E16" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="F16" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B17" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C17" t="s">
-        <v>215</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="E17" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="F17" t="s">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B18" t="s">
-        <v>219</v>
+        <v>157</v>
       </c>
       <c r="C18" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="E18" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F18" t="s">
-        <v>221</v>
+        <v>160</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>228</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>229</v>
       </c>
       <c r="D19" t="s">
         <v>141</v>
       </c>
       <c r="E19" t="s">
-        <v>174</v>
+        <v>230</v>
       </c>
       <c r="F19" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="E20" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="F20" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s">
-        <v>145</v>
+        <v>239</v>
       </c>
       <c r="C21" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
         <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>174</v>
+        <v>240</v>
       </c>
       <c r="F21" t="s">
-        <v>148</v>
+        <v>241</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>244</v>
       </c>
       <c r="C22" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="D22" t="s">
         <v>141</v>
       </c>
       <c r="E22" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F22" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="C23" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D23" t="s">
-        <v>238</v>
+        <v>141</v>
       </c>
       <c r="E23" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="F23" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C24" t="s">
-        <v>152</v>
+        <v>254</v>
       </c>
       <c r="D24" t="s">
         <v>141</v>
       </c>
       <c r="E24" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="F24" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>249</v>
+        <v>181</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>260</v>
       </c>
       <c r="E25" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="F25" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s">
-        <v>254</v>
+        <v>157</v>
       </c>
       <c r="C26" t="s">
-        <v>255</v>
+        <v>158</v>
       </c>
       <c r="D26" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="E26" t="s">
-        <v>154</v>
+        <v>265</v>
       </c>
       <c r="F26" t="s">
-        <v>256</v>
+        <v>160</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="C27" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="E27" t="s">
-        <v>260</v>
+        <v>143</v>
       </c>
       <c r="F27" t="s">
-        <v>261</v>
+        <v>194</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C28" t="s">
-        <v>265</v>
+        <v>140</v>
       </c>
       <c r="D28" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="E28" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="F28" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>277</v>
       </c>
       <c r="C29" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D29" t="s">
         <v>141</v>
       </c>
       <c r="E29" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F29" t="s">
-        <v>148</v>
+        <v>279</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s">
-        <v>204</v>
+        <v>282</v>
       </c>
       <c r="C30" t="s">
-        <v>273</v>
+        <v>140</v>
       </c>
       <c r="D30" t="s">
         <v>141</v>
       </c>
       <c r="E30" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="F30" t="s">
-        <v>154</v>
+        <v>284</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="C31" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>269</v>
       </c>
       <c r="E31" t="s">
-        <v>279</v>
+        <v>143</v>
       </c>
       <c r="F31" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C32" t="s">
-        <v>178</v>
+        <v>288</v>
       </c>
       <c r="D32" t="s">
-        <v>179</v>
+        <v>269</v>
       </c>
       <c r="E32" t="s">
-        <v>284</v>
+        <v>143</v>
       </c>
       <c r="F32" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>287</v>
+        <v>15</v>
       </c>
       <c r="B33" t="s">
+        <v>294</v>
+      </c>
+      <c r="C33" t="s">
+        <v>295</v>
+      </c>
+      <c r="D33" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" t="s">
+        <v>143</v>
+      </c>
+      <c r="F33" t="s">
+        <v>296</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>298</v>
+      </c>
+      <c r="B34" t="s">
+        <v>299</v>
+      </c>
+      <c r="C34" t="s">
+        <v>140</v>
+      </c>
+      <c r="D34" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F34" t="s">
+        <v>301</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>303</v>
+      </c>
+      <c r="B35" t="s">
+        <v>304</v>
+      </c>
+      <c r="C35" t="s">
+        <v>305</v>
+      </c>
+      <c r="D35" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" t="s">
+        <v>164</v>
+      </c>
+      <c r="F35" t="s">
+        <v>306</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>308</v>
+      </c>
+      <c r="B36" t="s">
+        <v>309</v>
+      </c>
+      <c r="C36" t="s">
+        <v>310</v>
+      </c>
+      <c r="D36" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" t="s">
+        <v>311</v>
+      </c>
+      <c r="F36" t="s">
+        <v>143</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>313</v>
+      </c>
+      <c r="B37" t="s">
+        <v>314</v>
+      </c>
+      <c r="C37" t="s">
+        <v>254</v>
+      </c>
+      <c r="D37" t="s">
+        <v>141</v>
+      </c>
+      <c r="E37" t="s">
+        <v>315</v>
+      </c>
+      <c r="F37" t="s">
+        <v>316</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>318</v>
+      </c>
+      <c r="B38" t="s">
+        <v>319</v>
+      </c>
+      <c r="C38" t="s">
+        <v>320</v>
+      </c>
+      <c r="D38" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" t="s">
+        <v>321</v>
+      </c>
+      <c r="F38" t="s">
+        <v>322</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>324</v>
+      </c>
+      <c r="B39" t="s">
+        <v>325</v>
+      </c>
+      <c r="C39" t="s">
+        <v>326</v>
+      </c>
+      <c r="D39" t="s">
+        <v>269</v>
+      </c>
+      <c r="E39" t="s">
+        <v>327</v>
+      </c>
+      <c r="F39" t="s">
+        <v>328</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>330</v>
+      </c>
+      <c r="B40" t="s">
+        <v>331</v>
+      </c>
+      <c r="C40" t="s">
+        <v>332</v>
+      </c>
+      <c r="D40" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40" t="s">
+        <v>333</v>
+      </c>
+      <c r="F40" t="s">
+        <v>334</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>336</v>
+      </c>
+      <c r="B41" t="s">
+        <v>337</v>
+      </c>
+      <c r="C41" t="s">
+        <v>140</v>
+      </c>
+      <c r="D41" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" t="s">
+        <v>338</v>
+      </c>
+      <c r="F41" t="s">
+        <v>339</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>341</v>
+      </c>
+      <c r="B42" t="s">
+        <v>342</v>
+      </c>
+      <c r="C42" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" t="s">
+        <v>343</v>
+      </c>
+      <c r="F42" t="s">
+        <v>344</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>346</v>
+      </c>
+      <c r="B43" t="s">
+        <v>347</v>
+      </c>
+      <c r="C43" t="s">
+        <v>348</v>
+      </c>
+      <c r="D43" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" t="s">
+        <v>349</v>
+      </c>
+      <c r="F43" t="s">
+        <v>350</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>352</v>
+      </c>
+      <c r="B44" t="s">
+        <v>353</v>
+      </c>
+      <c r="C44" t="s">
+        <v>181</v>
+      </c>
+      <c r="D44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E44" t="s">
+        <v>354</v>
+      </c>
+      <c r="F44" t="s">
+        <v>355</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>357</v>
+      </c>
+      <c r="B45" t="s">
+        <v>358</v>
+      </c>
+      <c r="C45" t="s">
+        <v>254</v>
+      </c>
+      <c r="D45" t="s">
+        <v>141</v>
+      </c>
+      <c r="E45" t="s">
+        <v>359</v>
+      </c>
+      <c r="F45" t="s">
+        <v>360</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>362</v>
+      </c>
+      <c r="B46" t="s">
+        <v>363</v>
+      </c>
+      <c r="C46" t="s">
+        <v>364</v>
+      </c>
+      <c r="D46" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" t="s">
+        <v>365</v>
+      </c>
+      <c r="F46" t="s">
+        <v>194</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>367</v>
+      </c>
+      <c r="B47" t="s">
+        <v>368</v>
+      </c>
+      <c r="C47" t="s">
+        <v>369</v>
+      </c>
+      <c r="D47" t="s">
+        <v>141</v>
+      </c>
+      <c r="E47" t="s">
+        <v>370</v>
+      </c>
+      <c r="F47" t="s">
+        <v>371</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>373</v>
+      </c>
+      <c r="B48" t="s">
+        <v>374</v>
+      </c>
+      <c r="C48" t="s">
+        <v>375</v>
+      </c>
+      <c r="D48" t="s">
+        <v>260</v>
+      </c>
+      <c r="E48" t="s">
+        <v>376</v>
+      </c>
+      <c r="F48" t="s">
+        <v>377</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>379</v>
+      </c>
+      <c r="B49" t="s">
+        <v>380</v>
+      </c>
+      <c r="C49" t="s">
+        <v>381</v>
+      </c>
+      <c r="D49" t="s">
+        <v>141</v>
+      </c>
+      <c r="E49" t="s">
+        <v>382</v>
+      </c>
+      <c r="F49" t="s">
+        <v>143</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>384</v>
+      </c>
+      <c r="B50" t="s">
+        <v>385</v>
+      </c>
+      <c r="C50" t="s">
+        <v>386</v>
+      </c>
+      <c r="D50" t="s">
+        <v>141</v>
+      </c>
+      <c r="E50" t="s">
+        <v>387</v>
+      </c>
+      <c r="F50" t="s">
+        <v>143</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>389</v>
+      </c>
+      <c r="B51" t="s">
+        <v>390</v>
+      </c>
+      <c r="C51" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" t="s">
+        <v>141</v>
+      </c>
+      <c r="E51" t="s">
+        <v>391</v>
+      </c>
+      <c r="F51" t="s">
+        <v>392</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>394</v>
+      </c>
+      <c r="B52" t="s">
+        <v>395</v>
+      </c>
+      <c r="C52" t="s">
+        <v>396</v>
+      </c>
+      <c r="D52" t="s">
+        <v>141</v>
+      </c>
+      <c r="E52" t="s">
+        <v>397</v>
+      </c>
+      <c r="F52" t="s">
+        <v>398</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>400</v>
+      </c>
+      <c r="B53" t="s">
+        <v>401</v>
+      </c>
+      <c r="C53" t="s">
+        <v>402</v>
+      </c>
+      <c r="D53" t="s">
+        <v>141</v>
+      </c>
+      <c r="E53" t="s">
+        <v>403</v>
+      </c>
+      <c r="F53" t="s">
+        <v>404</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>400</v>
+      </c>
+      <c r="B54" t="s">
+        <v>406</v>
+      </c>
+      <c r="C54" t="s">
+        <v>332</v>
+      </c>
+      <c r="D54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E54" t="s">
+        <v>391</v>
+      </c>
+      <c r="F54" t="s">
+        <v>407</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>409</v>
+      </c>
+      <c r="B55" t="s">
+        <v>410</v>
+      </c>
+      <c r="C55" t="s">
+        <v>411</v>
+      </c>
+      <c r="D55" t="s">
+        <v>141</v>
+      </c>
+      <c r="E55" t="s">
+        <v>412</v>
+      </c>
+      <c r="F55" t="s">
+        <v>413</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>415</v>
+      </c>
+      <c r="B56" t="s">
+        <v>416</v>
+      </c>
+      <c r="C56" t="s">
+        <v>181</v>
+      </c>
+      <c r="D56" t="s">
+        <v>141</v>
+      </c>
+      <c r="E56" t="s">
+        <v>417</v>
+      </c>
+      <c r="F56" t="s">
+        <v>418</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>420</v>
+      </c>
+      <c r="B57" t="s">
+        <v>421</v>
+      </c>
+      <c r="C57" t="s">
+        <v>422</v>
+      </c>
+      <c r="D57" t="s">
+        <v>141</v>
+      </c>
+      <c r="E57" t="s">
+        <v>423</v>
+      </c>
+      <c r="F57" t="s">
+        <v>424</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>426</v>
+      </c>
+      <c r="B58" t="s">
+        <v>427</v>
+      </c>
+      <c r="C58" t="s">
+        <v>428</v>
+      </c>
+      <c r="D58" t="s">
+        <v>141</v>
+      </c>
+      <c r="E58" t="s">
+        <v>429</v>
+      </c>
+      <c r="F58" t="s">
+        <v>430</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>432</v>
+      </c>
+      <c r="B59" t="s">
+        <v>433</v>
+      </c>
+      <c r="C59" t="s">
+        <v>140</v>
+      </c>
+      <c r="D59" t="s">
+        <v>141</v>
+      </c>
+      <c r="E59" t="s">
+        <v>434</v>
+      </c>
+      <c r="F59" t="s">
+        <v>435</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>437</v>
+      </c>
+      <c r="B60" t="s">
+        <v>438</v>
+      </c>
+      <c r="C60" t="s">
+        <v>439</v>
+      </c>
+      <c r="D60" t="s">
+        <v>141</v>
+      </c>
+      <c r="E60" t="s">
+        <v>440</v>
+      </c>
+      <c r="F60" t="s">
+        <v>218</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>442</v>
+      </c>
+      <c r="B61" t="s">
+        <v>443</v>
+      </c>
+      <c r="C61" t="s">
+        <v>444</v>
+      </c>
+      <c r="D61" t="s">
+        <v>141</v>
+      </c>
+      <c r="E61" t="s">
+        <v>445</v>
+      </c>
+      <c r="F61" t="s">
+        <v>446</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>448</v>
+      </c>
+      <c r="B62" t="s">
+        <v>449</v>
+      </c>
+      <c r="C62" t="s">
+        <v>140</v>
+      </c>
+      <c r="D62" t="s">
+        <v>141</v>
+      </c>
+      <c r="E62" t="s">
+        <v>450</v>
+      </c>
+      <c r="F62" t="s">
+        <v>451</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>453</v>
+      </c>
+      <c r="B63" t="s">
+        <v>454</v>
+      </c>
+      <c r="C63" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" t="s">
+        <v>141</v>
+      </c>
+      <c r="E63" t="s">
+        <v>455</v>
+      </c>
+      <c r="F63" t="s">
+        <v>456</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>458</v>
+      </c>
+      <c r="B64" t="s">
+        <v>459</v>
+      </c>
+      <c r="C64" t="s">
+        <v>460</v>
+      </c>
+      <c r="D64" t="s">
+        <v>141</v>
+      </c>
+      <c r="E64" t="s">
+        <v>461</v>
+      </c>
+      <c r="F64" t="s">
+        <v>462</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>464</v>
+      </c>
+      <c r="B65" t="s">
+        <v>465</v>
+      </c>
+      <c r="C65" t="s">
+        <v>140</v>
+      </c>
+      <c r="D65" t="s">
+        <v>269</v>
+      </c>
+      <c r="E65" t="s">
+        <v>466</v>
+      </c>
+      <c r="F65" t="s">
+        <v>467</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>469</v>
+      </c>
+      <c r="B66" t="s">
+        <v>470</v>
+      </c>
+      <c r="C66" t="s">
+        <v>254</v>
+      </c>
+      <c r="D66" t="s">
+        <v>141</v>
+      </c>
+      <c r="E66" t="s">
+        <v>471</v>
+      </c>
+      <c r="F66" t="s">
+        <v>472</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>474</v>
+      </c>
+      <c r="B67" t="s">
+        <v>470</v>
+      </c>
+      <c r="C67" t="s">
+        <v>254</v>
+      </c>
+      <c r="D67" t="s">
+        <v>141</v>
+      </c>
+      <c r="E67" t="s">
+        <v>475</v>
+      </c>
+      <c r="F67" t="s">
+        <v>143</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>477</v>
+      </c>
+      <c r="B68" t="s">
+        <v>478</v>
+      </c>
+      <c r="C68" t="s">
+        <v>305</v>
+      </c>
+      <c r="D68" t="s">
+        <v>141</v>
+      </c>
+      <c r="E68" t="s">
+        <v>479</v>
+      </c>
+      <c r="F68" t="s">
+        <v>143</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>481</v>
+      </c>
+      <c r="B69" t="s">
+        <v>478</v>
+      </c>
+      <c r="C69" t="s">
+        <v>305</v>
+      </c>
+      <c r="D69" t="s">
+        <v>141</v>
+      </c>
+      <c r="E69" t="s">
+        <v>482</v>
+      </c>
+      <c r="F69" t="s">
+        <v>143</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>484</v>
+      </c>
+      <c r="B70" t="s">
+        <v>485</v>
+      </c>
+      <c r="C70" t="s">
+        <v>486</v>
+      </c>
+      <c r="D70" t="s">
+        <v>141</v>
+      </c>
+      <c r="E70" t="s">
+        <v>487</v>
+      </c>
+      <c r="F70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>490</v>
+      </c>
+      <c r="B71" t="s">
+        <v>491</v>
+      </c>
+      <c r="C71" t="s">
+        <v>492</v>
+      </c>
+      <c r="D71" t="s">
+        <v>269</v>
+      </c>
+      <c r="E71" t="s">
+        <v>143</v>
+      </c>
+      <c r="F71" t="s">
+        <v>493</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>495</v>
+      </c>
+      <c r="B72" t="s">
+        <v>496</v>
+      </c>
+      <c r="C72" t="s">
+        <v>381</v>
+      </c>
+      <c r="D72" t="s">
+        <v>141</v>
+      </c>
+      <c r="E72" t="s">
+        <v>497</v>
+      </c>
+      <c r="F72" t="s">
+        <v>498</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>495</v>
+      </c>
+      <c r="B73" t="s">
+        <v>496</v>
+      </c>
+      <c r="C73" t="s">
+        <v>187</v>
+      </c>
+      <c r="D73" t="s">
+        <v>141</v>
+      </c>
+      <c r="E73" t="s">
+        <v>497</v>
+      </c>
+      <c r="F73" t="s">
+        <v>498</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>501</v>
+      </c>
+      <c r="B74" t="s">
+        <v>502</v>
+      </c>
+      <c r="C74" t="s">
+        <v>140</v>
+      </c>
+      <c r="D74" t="s">
+        <v>269</v>
+      </c>
+      <c r="E74" t="s">
+        <v>503</v>
+      </c>
+      <c r="F74" t="s">
+        <v>504</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>506</v>
+      </c>
+      <c r="B75" t="s">
+        <v>157</v>
+      </c>
+      <c r="C75" t="s">
+        <v>158</v>
+      </c>
+      <c r="D75" t="s">
+        <v>141</v>
+      </c>
+      <c r="E75" t="s">
+        <v>265</v>
+      </c>
+      <c r="F75" t="s">
+        <v>507</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>509</v>
+      </c>
+      <c r="B76" t="s">
+        <v>191</v>
+      </c>
+      <c r="C76" t="s">
+        <v>192</v>
+      </c>
+      <c r="D76" t="s">
+        <v>141</v>
+      </c>
+      <c r="E76" t="s">
+        <v>510</v>
+      </c>
+      <c r="F76" t="s">
+        <v>194</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>512</v>
+      </c>
+      <c r="B77" t="s">
+        <v>513</v>
+      </c>
+      <c r="C77" t="s">
+        <v>140</v>
+      </c>
+      <c r="D77" t="s">
+        <v>141</v>
+      </c>
+      <c r="E77" t="s">
+        <v>514</v>
+      </c>
+      <c r="F77" t="s">
+        <v>515</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>517</v>
+      </c>
+      <c r="B78" t="s">
+        <v>518</v>
+      </c>
+      <c r="C78" t="s">
+        <v>519</v>
+      </c>
+      <c r="D78" t="s">
+        <v>141</v>
+      </c>
+      <c r="E78" t="s">
+        <v>143</v>
+      </c>
+      <c r="F78" t="s">
+        <v>143</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>521</v>
+      </c>
+      <c r="B79" t="s">
+        <v>522</v>
+      </c>
+      <c r="C79" t="s">
+        <v>523</v>
+      </c>
+      <c r="D79" t="s">
+        <v>141</v>
+      </c>
+      <c r="E79" t="s">
+        <v>524</v>
+      </c>
+      <c r="F79" t="s">
+        <v>525</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>527</v>
+      </c>
+      <c r="B80" t="s">
+        <v>528</v>
+      </c>
+      <c r="C80" t="s">
+        <v>529</v>
+      </c>
+      <c r="D80" t="s">
+        <v>141</v>
+      </c>
+      <c r="E80" t="s">
+        <v>530</v>
+      </c>
+      <c r="F80" t="s">
+        <v>531</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>533</v>
+      </c>
+      <c r="B81" t="s">
+        <v>253</v>
+      </c>
+      <c r="C81" t="s">
+        <v>254</v>
+      </c>
+      <c r="D81" t="s">
+        <v>141</v>
+      </c>
+      <c r="E81" t="s">
+        <v>397</v>
+      </c>
+      <c r="F81" t="s">
+        <v>256</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>535</v>
+      </c>
+      <c r="B82" t="s">
+        <v>536</v>
+      </c>
+      <c r="C82" t="s">
+        <v>537</v>
+      </c>
+      <c r="D82" t="s">
+        <v>199</v>
+      </c>
+      <c r="E82" t="s">
+        <v>143</v>
+      </c>
+      <c r="F82" t="s">
+        <v>538</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>540</v>
+      </c>
+      <c r="B83" t="s">
+        <v>541</v>
+      </c>
+      <c r="C83" t="s">
+        <v>348</v>
+      </c>
+      <c r="D83" t="s">
+        <v>141</v>
+      </c>
+      <c r="E83" t="s">
+        <v>542</v>
+      </c>
+      <c r="F83" t="s">
+        <v>543</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>545</v>
+      </c>
+      <c r="B84" t="s">
+        <v>410</v>
+      </c>
+      <c r="C84" t="s">
+        <v>411</v>
+      </c>
+      <c r="D84" t="s">
+        <v>141</v>
+      </c>
+      <c r="E84" t="s">
+        <v>546</v>
+      </c>
+      <c r="F84" t="s">
+        <v>413</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>548</v>
+      </c>
+      <c r="B85" t="s">
+        <v>549</v>
+      </c>
+      <c r="C85" t="s">
+        <v>175</v>
+      </c>
+      <c r="D85" t="s">
+        <v>141</v>
+      </c>
+      <c r="E85" t="s">
+        <v>550</v>
+      </c>
+      <c r="F85" t="s">
+        <v>551</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>553</v>
+      </c>
+      <c r="B86" t="s">
+        <v>157</v>
+      </c>
+      <c r="C86" t="s">
+        <v>158</v>
+      </c>
+      <c r="D86" t="s">
+        <v>141</v>
+      </c>
+      <c r="E86" t="s">
+        <v>265</v>
+      </c>
+      <c r="F86" t="s">
+        <v>160</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>555</v>
+      </c>
+      <c r="B87" t="s">
+        <v>157</v>
+      </c>
+      <c r="C87" t="s">
+        <v>158</v>
+      </c>
+      <c r="D87" t="s">
+        <v>141</v>
+      </c>
+      <c r="E87" t="s">
+        <v>265</v>
+      </c>
+      <c r="F87" t="s">
+        <v>160</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>557</v>
+      </c>
+      <c r="B88" t="s">
+        <v>558</v>
+      </c>
+      <c r="C88" t="s">
+        <v>559</v>
+      </c>
+      <c r="D88" t="s">
+        <v>260</v>
+      </c>
+      <c r="E88" t="s">
+        <v>560</v>
+      </c>
+      <c r="F88" t="s">
+        <v>561</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>563</v>
+      </c>
+      <c r="B89" t="s">
+        <v>564</v>
+      </c>
+      <c r="C89" t="s">
+        <v>187</v>
+      </c>
+      <c r="D89" t="s">
+        <v>141</v>
+      </c>
+      <c r="E89" t="s">
+        <v>565</v>
+      </c>
+      <c r="F89" t="s">
+        <v>566</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>568</v>
+      </c>
+      <c r="B90" t="s">
+        <v>569</v>
+      </c>
+      <c r="C90" t="s">
+        <v>153</v>
+      </c>
+      <c r="D90" t="s">
+        <v>141</v>
+      </c>
+      <c r="E90" t="s">
+        <v>570</v>
+      </c>
+      <c r="F90" t="s">
+        <v>571</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>573</v>
+      </c>
+      <c r="B91" t="s">
+        <v>574</v>
+      </c>
+      <c r="C91" t="s">
+        <v>181</v>
+      </c>
+      <c r="D91" t="s">
+        <v>141</v>
+      </c>
+      <c r="E91" t="s">
+        <v>475</v>
+      </c>
+      <c r="F91" t="s">
+        <v>575</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>577</v>
+      </c>
+      <c r="B92" t="s">
+        <v>578</v>
+      </c>
+      <c r="C92" t="s">
+        <v>579</v>
+      </c>
+      <c r="D92" t="s">
+        <v>141</v>
+      </c>
+      <c r="E92" t="s">
+        <v>445</v>
+      </c>
+      <c r="F92" t="s">
+        <v>580</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>577</v>
+      </c>
+      <c r="B93" t="s">
+        <v>578</v>
+      </c>
+      <c r="C93" t="s">
+        <v>582</v>
+      </c>
+      <c r="D93" t="s">
+        <v>141</v>
+      </c>
+      <c r="E93" t="s">
+        <v>445</v>
+      </c>
+      <c r="F93" t="s">
+        <v>580</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>584</v>
+      </c>
+      <c r="B94" t="s">
+        <v>585</v>
+      </c>
+      <c r="C94" t="s">
+        <v>140</v>
+      </c>
+      <c r="D94" t="s">
+        <v>260</v>
+      </c>
+      <c r="E94" t="s">
+        <v>586</v>
+      </c>
+      <c r="F94" t="s">
+        <v>587</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>589</v>
+      </c>
+      <c r="B95" t="s">
+        <v>590</v>
+      </c>
+      <c r="C95" t="s">
+        <v>187</v>
+      </c>
+      <c r="D95" t="s">
+        <v>141</v>
+      </c>
+      <c r="E95" t="s">
+        <v>591</v>
+      </c>
+      <c r="F95" t="s">
+        <v>592</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>594</v>
+      </c>
+      <c r="B96" t="s">
+        <v>595</v>
+      </c>
+      <c r="C96" t="s">
+        <v>596</v>
+      </c>
+      <c r="D96" t="s">
+        <v>141</v>
+      </c>
+      <c r="E96" t="s">
+        <v>597</v>
+      </c>
+      <c r="F96" t="s">
+        <v>284</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>599</v>
+      </c>
+      <c r="B97" t="s">
+        <v>253</v>
+      </c>
+      <c r="C97" t="s">
+        <v>600</v>
+      </c>
+      <c r="D97" t="s">
+        <v>141</v>
+      </c>
+      <c r="E97" t="s">
+        <v>601</v>
+      </c>
+      <c r="F97" t="s">
+        <v>256</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>603</v>
+      </c>
+      <c r="B98" t="s">
+        <v>604</v>
+      </c>
+      <c r="C98" t="s">
+        <v>140</v>
+      </c>
+      <c r="D98" t="s">
+        <v>141</v>
+      </c>
+      <c r="E98" t="s">
+        <v>605</v>
+      </c>
+      <c r="F98" t="s">
+        <v>344</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>607</v>
+      </c>
+      <c r="B99" t="s">
+        <v>608</v>
+      </c>
+      <c r="C99" t="s">
+        <v>28</v>
+      </c>
+      <c r="D99" t="s">
+        <v>141</v>
+      </c>
+      <c r="E99" t="s">
+        <v>609</v>
+      </c>
+      <c r="F99" t="s">
+        <v>610</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>612</v>
+      </c>
+      <c r="B100" t="s">
+        <v>613</v>
+      </c>
+      <c r="C100" t="s">
+        <v>614</v>
+      </c>
+      <c r="D100" t="s">
+        <v>141</v>
+      </c>
+      <c r="E100" t="s">
+        <v>615</v>
+      </c>
+      <c r="F100" t="s">
+        <v>616</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>618</v>
+      </c>
+      <c r="B101" t="s">
+        <v>619</v>
+      </c>
+      <c r="C101" t="s">
+        <v>620</v>
+      </c>
+      <c r="D101" t="s">
+        <v>141</v>
+      </c>
+      <c r="E101" t="s">
+        <v>621</v>
+      </c>
+      <c r="F101" t="s">
+        <v>622</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>624</v>
+      </c>
+      <c r="B102" t="s">
+        <v>625</v>
+      </c>
+      <c r="C102" t="s">
+        <v>626</v>
+      </c>
+      <c r="D102" t="s">
+        <v>141</v>
+      </c>
+      <c r="E102" t="s">
+        <v>627</v>
+      </c>
+      <c r="F102" t="s">
+        <v>628</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>630</v>
+      </c>
+      <c r="B103" t="s">
+        <v>631</v>
+      </c>
+      <c r="C103" t="s">
+        <v>632</v>
+      </c>
+      <c r="D103" t="s">
+        <v>141</v>
+      </c>
+      <c r="E103" t="s">
+        <v>633</v>
+      </c>
+      <c r="F103" t="s">
+        <v>634</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>636</v>
+      </c>
+      <c r="B104" t="s">
+        <v>637</v>
+      </c>
+      <c r="C104" t="s">
         <v>288</v>
       </c>
-      <c r="C33" t="s">
-        <v>289</v>
-      </c>
-      <c r="D33" t="s">
-        <v>179</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="D104" t="s">
+        <v>269</v>
+      </c>
+      <c r="E104" t="s">
+        <v>143</v>
+      </c>
+      <c r="F104" t="s">
+        <v>171</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>639</v>
+      </c>
+      <c r="B105" t="s">
+        <v>640</v>
+      </c>
+      <c r="C105" t="s">
+        <v>153</v>
+      </c>
+      <c r="D105" t="s">
+        <v>141</v>
+      </c>
+      <c r="E105" t="s">
+        <v>641</v>
+      </c>
+      <c r="F105" t="s">
+        <v>642</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>644</v>
+      </c>
+      <c r="B106" t="s">
+        <v>470</v>
+      </c>
+      <c r="C106" t="s">
+        <v>254</v>
+      </c>
+      <c r="D106" t="s">
+        <v>141</v>
+      </c>
+      <c r="E106" t="s">
+        <v>255</v>
+      </c>
+      <c r="F106" t="s">
+        <v>645</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>647</v>
+      </c>
+      <c r="B107" t="s">
+        <v>648</v>
+      </c>
+      <c r="C107" t="s">
+        <v>140</v>
+      </c>
+      <c r="D107" t="s">
+        <v>260</v>
+      </c>
+      <c r="E107" t="s">
+        <v>649</v>
+      </c>
+      <c r="F107" t="s">
+        <v>451</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>647</v>
+      </c>
+      <c r="B108" t="s">
+        <v>640</v>
+      </c>
+      <c r="C108" t="s">
+        <v>153</v>
+      </c>
+      <c r="D108" t="s">
+        <v>141</v>
+      </c>
+      <c r="E108" t="s">
+        <v>651</v>
+      </c>
+      <c r="F108" t="s">
+        <v>642</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>653</v>
+      </c>
+      <c r="B109" t="s">
+        <v>654</v>
+      </c>
+      <c r="C109" t="s">
+        <v>254</v>
+      </c>
+      <c r="D109" t="s">
+        <v>141</v>
+      </c>
+      <c r="E109" t="s">
+        <v>655</v>
+      </c>
+      <c r="F109" t="s">
+        <v>143</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>657</v>
+      </c>
+      <c r="B110" t="s">
+        <v>658</v>
+      </c>
+      <c r="C110" t="s">
+        <v>659</v>
+      </c>
+      <c r="D110" t="s">
+        <v>199</v>
+      </c>
+      <c r="E110" t="s">
+        <v>660</v>
+      </c>
+      <c r="F110" t="s">
+        <v>661</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>663</v>
+      </c>
+      <c r="B111" t="s">
+        <v>664</v>
+      </c>
+      <c r="C111" t="s">
+        <v>665</v>
+      </c>
+      <c r="D111" t="s">
+        <v>269</v>
+      </c>
+      <c r="E111" t="s">
+        <v>666</v>
+      </c>
+      <c r="F111" t="s">
+        <v>322</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>668</v>
+      </c>
+      <c r="B112" t="s">
+        <v>157</v>
+      </c>
+      <c r="C112" t="s">
+        <v>158</v>
+      </c>
+      <c r="D112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E112" t="s">
+        <v>669</v>
+      </c>
+      <c r="F112" t="s">
+        <v>160</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>671</v>
+      </c>
+      <c r="B113" t="s">
+        <v>672</v>
+      </c>
+      <c r="C113" t="s">
+        <v>140</v>
+      </c>
+      <c r="D113" t="s">
+        <v>141</v>
+      </c>
+      <c r="E113" t="s">
+        <v>673</v>
+      </c>
+      <c r="F113" t="s">
+        <v>674</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>676</v>
+      </c>
+      <c r="B114" t="s">
+        <v>677</v>
+      </c>
+      <c r="C114" t="s">
+        <v>140</v>
+      </c>
+      <c r="D114" t="s">
+        <v>141</v>
+      </c>
+      <c r="E114" t="s">
+        <v>678</v>
+      </c>
+      <c r="F114" t="s">
+        <v>679</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>681</v>
+      </c>
+      <c r="B115" t="s">
+        <v>625</v>
+      </c>
+      <c r="C115" t="s">
+        <v>626</v>
+      </c>
+      <c r="D115" t="s">
+        <v>260</v>
+      </c>
+      <c r="E115" t="s">
+        <v>682</v>
+      </c>
+      <c r="F115" t="s">
+        <v>628</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>684</v>
+      </c>
+      <c r="B116" t="s">
+        <v>139</v>
+      </c>
+      <c r="C116" t="s">
+        <v>140</v>
+      </c>
+      <c r="D116" t="s">
+        <v>141</v>
+      </c>
+      <c r="E116" t="s">
+        <v>685</v>
+      </c>
+      <c r="F116" t="s">
+        <v>143</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>687</v>
+      </c>
+      <c r="B117" t="s">
+        <v>688</v>
+      </c>
+      <c r="C117" t="s">
+        <v>254</v>
+      </c>
+      <c r="D117" t="s">
+        <v>141</v>
+      </c>
+      <c r="E117" t="s">
+        <v>689</v>
+      </c>
+      <c r="F117" t="s">
+        <v>690</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>692</v>
+      </c>
+      <c r="B118" t="s">
+        <v>693</v>
+      </c>
+      <c r="C118" t="s">
+        <v>254</v>
+      </c>
+      <c r="D118" t="s">
+        <v>141</v>
+      </c>
+      <c r="E118" t="s">
+        <v>694</v>
+      </c>
+      <c r="F118" t="s">
+        <v>695</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>697</v>
+      </c>
+      <c r="B119" t="s">
+        <v>139</v>
+      </c>
+      <c r="C119" t="s">
+        <v>140</v>
+      </c>
+      <c r="D119" t="s">
+        <v>141</v>
+      </c>
+      <c r="E119" t="s">
+        <v>698</v>
+      </c>
+      <c r="F119" t="s">
+        <v>143</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>700</v>
+      </c>
+      <c r="B120" t="s">
+        <v>454</v>
+      </c>
+      <c r="C120" t="s">
+        <v>701</v>
+      </c>
+      <c r="D120" t="s">
+        <v>141</v>
+      </c>
+      <c r="E120" t="s">
+        <v>702</v>
+      </c>
+      <c r="F120" t="s">
+        <v>143</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>704</v>
+      </c>
+      <c r="B121" t="s">
+        <v>152</v>
+      </c>
+      <c r="C121" t="s">
+        <v>153</v>
+      </c>
+      <c r="D121" t="s">
+        <v>141</v>
+      </c>
+      <c r="E121" t="s">
         <v>154</v>
       </c>
-      <c r="F33" t="s">
-        <v>290</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>291</v>
+      <c r="F121" t="s">
+        <v>155</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>706</v>
+      </c>
+      <c r="B122" t="s">
+        <v>688</v>
+      </c>
+      <c r="C122" t="s">
+        <v>707</v>
+      </c>
+      <c r="D122" t="s">
+        <v>141</v>
+      </c>
+      <c r="E122" t="s">
+        <v>708</v>
+      </c>
+      <c r="F122" t="s">
+        <v>690</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>710</v>
+      </c>
+      <c r="B123" t="s">
+        <v>470</v>
+      </c>
+      <c r="C123" t="s">
+        <v>254</v>
+      </c>
+      <c r="D123" t="s">
+        <v>141</v>
+      </c>
+      <c r="E123" t="s">
+        <v>255</v>
+      </c>
+      <c r="F123" t="s">
+        <v>543</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>712</v>
+      </c>
+      <c r="B124" t="s">
+        <v>713</v>
+      </c>
+      <c r="C124" t="s">
+        <v>714</v>
+      </c>
+      <c r="D124" t="s">
+        <v>141</v>
+      </c>
+      <c r="E124" t="s">
+        <v>475</v>
+      </c>
+      <c r="F124" t="s">
+        <v>715</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>717</v>
+      </c>
+      <c r="B125" t="s">
+        <v>718</v>
+      </c>
+      <c r="C125" t="s">
+        <v>719</v>
+      </c>
+      <c r="D125" t="s">
+        <v>141</v>
+      </c>
+      <c r="E125" t="s">
+        <v>720</v>
+      </c>
+      <c r="F125" t="s">
+        <v>721</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>723</v>
+      </c>
+      <c r="B126" t="s">
+        <v>608</v>
+      </c>
+      <c r="C126" t="s">
+        <v>28</v>
+      </c>
+      <c r="D126" t="s">
+        <v>141</v>
+      </c>
+      <c r="E126" t="s">
+        <v>724</v>
+      </c>
+      <c r="F126" t="s">
+        <v>610</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>726</v>
+      </c>
+      <c r="B127" t="s">
+        <v>727</v>
+      </c>
+      <c r="C127" t="s">
+        <v>140</v>
+      </c>
+      <c r="D127" t="s">
+        <v>269</v>
+      </c>
+      <c r="E127" t="s">
+        <v>728</v>
+      </c>
+      <c r="F127" t="s">
+        <v>729</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>731</v>
+      </c>
+      <c r="B128" t="s">
+        <v>732</v>
+      </c>
+      <c r="C128" t="s">
+        <v>140</v>
+      </c>
+      <c r="D128" t="s">
+        <v>141</v>
+      </c>
+      <c r="E128" t="s">
+        <v>733</v>
+      </c>
+      <c r="F128" t="s">
+        <v>734</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>736</v>
+      </c>
+      <c r="B129" t="s">
+        <v>564</v>
+      </c>
+      <c r="C129" t="s">
+        <v>614</v>
+      </c>
+      <c r="D129" t="s">
+        <v>141</v>
+      </c>
+      <c r="E129" t="s">
+        <v>737</v>
+      </c>
+      <c r="F129" t="s">
+        <v>738</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>740</v>
+      </c>
+      <c r="B130" t="s">
+        <v>741</v>
+      </c>
+      <c r="C130" t="s">
+        <v>140</v>
+      </c>
+      <c r="D130" t="s">
+        <v>141</v>
+      </c>
+      <c r="E130" t="s">
+        <v>742</v>
+      </c>
+      <c r="F130" t="s">
+        <v>743</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>745</v>
+      </c>
+      <c r="B131" t="s">
+        <v>746</v>
+      </c>
+      <c r="C131" t="s">
+        <v>747</v>
+      </c>
+      <c r="D131" t="s">
+        <v>269</v>
+      </c>
+      <c r="E131" t="s">
+        <v>143</v>
+      </c>
+      <c r="F131" t="s">
+        <v>748</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>750</v>
+      </c>
+      <c r="B132" t="s">
+        <v>751</v>
+      </c>
+      <c r="C132" t="s">
+        <v>254</v>
+      </c>
+      <c r="D132" t="s">
+        <v>141</v>
+      </c>
+      <c r="E132" t="s">
+        <v>752</v>
+      </c>
+      <c r="F132" t="s">
+        <v>753</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -2735,6 +6401,105 @@
     <hyperlink ref="H31" r:id="rId30"/>
     <hyperlink ref="H32" r:id="rId31"/>
     <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-28.xlsx
+++ b/docs/xlsx/jobs-2026-08-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="785">
   <si>
     <t>Title</t>
   </si>
@@ -502,6 +502,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/29ea5c4273604a05ae71baa1ab1568c3-administrative-assistant-springwell-inc-waltham</t>
   </si>
   <si>
+    <t>Lambert House LGBTQ Youth Center in Seattle, WA</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 4583.00 - 5666.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa08753883e2489994119cfd86fa4278-administrative-assistant-lambert-house-lgbtq-youth-center-in-seattle-wa-seattle</t>
+  </si>
+  <si>
     <t>Administrative Assistant, Climate Change &amp; Environmental Justice</t>
   </si>
   <si>
@@ -772,6 +787,21 @@
     <t>https://www.idealist.org/en/job/78f95f77d98542b6a64736ecebba8ad3-associate-organizer-common-ground-tenants-united-milwaukee</t>
   </si>
   <si>
+    <t>Bilingual Customer Service Representative</t>
+  </si>
+  <si>
+    <t>Esperanza, Inc.</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Race Ethnicity, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0067bdfe6f0c44d9a51fd57facc9f4fd-bilingual-customer-service-representative-esperanza-inc-cleveland</t>
+  </si>
+  <si>
     <t>Bilingual Licensed Mental Health Counselor</t>
   </si>
   <si>
@@ -829,6 +859,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/c78109688acb4f50b976b1ecf23d97cd-bookkeeperaccountant-partners-for-andean-community-health-west-hartford</t>
   </si>
   <si>
+    <t>Bronx Site Director</t>
+  </si>
+  <si>
+    <t>Grand Street Settlement</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 87000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c63b3bc4e27466d94cff0acf4c4d4d2-bronx-site-director-grand-street-settlement-bronx-county</t>
+  </si>
+  <si>
     <t>Business Immigration Associate</t>
   </si>
   <si>
@@ -910,6 +958,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/1686d83c304f43f2a19d11c796147f2e-chief-executive-officer-disability-rights-new-mexico-albuquerque</t>
   </si>
   <si>
+    <t>El Pasoans Fighting Hunger Food Bank</t>
+  </si>
+  <si>
+    <t>El Paso, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4a0c7d0a88264f61b0df4e3a98e17a27-chief-executive-officer-el-pasoans-fighting-hunger-food-bank-el-paso</t>
+  </si>
+  <si>
     <t>Chief Operating Officer</t>
   </si>
   <si>
@@ -1012,9 +1069,6 @@
     <t>Washington Conservation Action</t>
   </si>
   <si>
-    <t>Seattle, Washington</t>
-  </si>
-  <si>
     <t>USD 73000.00 - 73000.00/year</t>
   </si>
   <si>
@@ -1816,15 +1870,24 @@
     <t>NY Connects Benefits Counselor - Bronx</t>
   </si>
   <si>
-    <t>Bronx County, New York</t>
-  </si>
-  <si>
     <t>USD 55000.00 - 55000.00/year</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/da1f0115aa044567aed876757cbb0980-ny-connects-benefits-counselor-bronx-center-for-independence-of-the-disabled-ny-bronx-county</t>
   </si>
   <si>
+    <t>Operations Coordinator</t>
+  </si>
+  <si>
+    <t>USGBC California</t>
+  </si>
+  <si>
+    <t>Southern California, Maryland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/620219d4b62f4e83a355973572d4b84d-operations-coordinator-usgbc-california-southern-california</t>
+  </si>
+  <si>
     <t>Operations Manager</t>
   </si>
   <si>
@@ -2068,6 +2131,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/45ac74e6c0ee4548b1be588cc5a99bbb-sane-coordinator-respect-together-harrisburg</t>
   </si>
   <si>
+    <t>Self Contained Elementary Special Education Lead Teacher</t>
+  </si>
+  <si>
+    <t>Bridges Public Charter School</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Disability, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5b4310bd8d842d096f3f866039fb19a-self-contained-elementary-special-education-lead-teacher-bridges-public-charter-school-washington</t>
+  </si>
+  <si>
     <t>Senior Account Director (Direct Marketing, Non-Profit Fundraising)</t>
   </si>
   <si>
@@ -2119,9 +2200,6 @@
     <t>Senior Director for Philanthropic Engagement</t>
   </si>
   <si>
-    <t>Washington, DC</t>
-  </si>
-  <si>
     <t>USD 130000.00 - 150000.00/year</t>
   </si>
   <si>
@@ -2150,6 +2228,18 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/06c34e6e875b4fee9c4475f0757bf62b-sheva-center-communication-technology-and-operations-associate-jcc-association-new-york</t>
+  </si>
+  <si>
+    <t>Spanish speaking SPED ABA Teacher Assistant (ELEM)</t>
+  </si>
+  <si>
+    <t>USD 36000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2fe88626f5dd41afb0c7d8513fae50f8-spanish-speaking-sped-aba-teacher-assistant-elem-bridges-public-charter-school-washington</t>
   </si>
   <si>
     <t>St. Johns Riverkeeper</t>
@@ -3314,7 +3404,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3447,13 +3537,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
         <v>162</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>163</v>
-      </c>
-      <c r="C6" t="s">
-        <v>140</v>
       </c>
       <c r="D6" t="s">
         <v>141</v>
@@ -3476,85 +3566,85 @@
         <v>168</v>
       </c>
       <c r="C7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" t="s">
         <v>169</v>
       </c>
-      <c r="D7" t="s">
-        <v>141</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>170</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" t="s">
         <v>173</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>174</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8" t="s">
         <v>175</v>
       </c>
-      <c r="D8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>176</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" t="s">
         <v>179</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>180</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" t="s">
         <v>181</v>
       </c>
-      <c r="D9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>182</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" t="s">
         <v>185</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>186</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" t="s">
         <v>187</v>
       </c>
-      <c r="D10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>188</v>
-      </c>
-      <c r="F10" t="s">
-        <v>143</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>189</v>
@@ -3577,99 +3667,99 @@
         <v>193</v>
       </c>
       <c r="F11" t="s">
+        <v>143</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B12" t="s">
         <v>196</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>197</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" t="s">
         <v>198</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>199</v>
       </c>
-      <c r="E12" t="s">
-        <v>143</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="H12" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B13" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D13" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E13" t="s">
         <v>143</v>
       </c>
       <c r="F13" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D14" t="s">
         <v>204</v>
       </c>
-      <c r="B14" t="s">
+      <c r="E14" t="s">
+        <v>143</v>
+      </c>
+      <c r="F14" t="s">
         <v>205</v>
       </c>
-      <c r="C14" t="s">
-        <v>206</v>
-      </c>
-      <c r="D14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E14" t="s">
-        <v>207</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="H14" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" t="s">
         <v>210</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>211</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" t="s">
         <v>212</v>
       </c>
-      <c r="D15" t="s">
-        <v>141</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>213</v>
-      </c>
-      <c r="F15" t="s">
-        <v>143</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>214</v>
@@ -3683,16 +3773,16 @@
         <v>216</v>
       </c>
       <c r="C16" t="s">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="D16" t="s">
         <v>141</v>
       </c>
       <c r="E16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F16" t="s">
-        <v>218</v>
+        <v>143</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>219</v>
@@ -3715,44 +3805,44 @@
         <v>222</v>
       </c>
       <c r="F17" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="C18" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="D18" t="s">
         <v>141</v>
       </c>
       <c r="E18" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F18" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="C19" t="s">
-        <v>229</v>
+        <v>158</v>
       </c>
       <c r="D19" t="s">
         <v>141</v>
@@ -3761,27 +3851,27 @@
         <v>230</v>
       </c>
       <c r="F19" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B20" t="s">
         <v>233</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>234</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" t="s">
         <v>235</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" t="s">
-        <v>170</v>
       </c>
       <c r="F20" t="s">
         <v>236</v>
@@ -3798,13 +3888,13 @@
         <v>239</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="D21" t="s">
         <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="F21" t="s">
         <v>241</v>
@@ -3821,99 +3911,99 @@
         <v>244</v>
       </c>
       <c r="C22" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="D22" t="s">
         <v>141</v>
       </c>
       <c r="E22" t="s">
-        <v>143</v>
+        <v>245</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>246</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C23" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D23" t="s">
         <v>141</v>
       </c>
       <c r="E23" t="s">
-        <v>249</v>
+        <v>143</v>
       </c>
       <c r="F23" t="s">
+        <v>143</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>251</v>
+      </c>
+      <c r="B24" t="s">
         <v>252</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>253</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" t="s">
         <v>254</v>
       </c>
-      <c r="D24" t="s">
-        <v>141</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>255</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>257</v>
+      </c>
+      <c r="B25" t="s">
         <v>258</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" t="s">
         <v>259</v>
       </c>
-      <c r="C25" t="s">
-        <v>181</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>260</v>
       </c>
-      <c r="E25" t="s">
+      <c r="H25" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="F25" t="s">
-        <v>262</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>262</v>
+      </c>
+      <c r="B26" t="s">
+        <v>263</v>
+      </c>
+      <c r="C26" t="s">
         <v>264</v>
-      </c>
-      <c r="B26" t="s">
-        <v>157</v>
-      </c>
-      <c r="C26" t="s">
-        <v>158</v>
       </c>
       <c r="D26" t="s">
         <v>141</v>
@@ -3922,76 +4012,76 @@
         <v>265</v>
       </c>
       <c r="F26" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="D27" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E27" t="s">
-        <v>143</v>
+        <v>271</v>
       </c>
       <c r="F27" t="s">
-        <v>194</v>
+        <v>272</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s">
-        <v>272</v>
+        <v>157</v>
       </c>
       <c r="C28" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="D28" t="s">
         <v>141</v>
       </c>
       <c r="E28" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F28" t="s">
-        <v>274</v>
+        <v>160</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C29" t="s">
         <v>140</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>279</v>
       </c>
       <c r="E29" t="s">
-        <v>278</v>
+        <v>143</v>
       </c>
       <c r="F29" t="s">
-        <v>279</v>
+        <v>199</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>280</v>
@@ -4005,881 +4095,881 @@
         <v>282</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>283</v>
       </c>
       <c r="D30" t="s">
         <v>141</v>
       </c>
       <c r="E30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B31" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C31" t="s">
-        <v>288</v>
+        <v>140</v>
       </c>
       <c r="D31" t="s">
-        <v>269</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s">
-        <v>143</v>
+        <v>289</v>
       </c>
       <c r="F31" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C32" t="s">
-        <v>288</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>269</v>
+        <v>141</v>
       </c>
       <c r="E32" t="s">
-        <v>143</v>
+        <v>294</v>
       </c>
       <c r="F32" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C33" t="s">
-        <v>295</v>
+        <v>140</v>
       </c>
       <c r="D33" t="s">
         <v>141</v>
       </c>
       <c r="E33" t="s">
-        <v>143</v>
+        <v>299</v>
       </c>
       <c r="F33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="D34" t="s">
-        <v>141</v>
+        <v>279</v>
       </c>
       <c r="E34" t="s">
-        <v>300</v>
+        <v>143</v>
       </c>
       <c r="F34" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>307</v>
+      </c>
+      <c r="B35" t="s">
         <v>303</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>304</v>
       </c>
-      <c r="C35" t="s">
-        <v>305</v>
-      </c>
       <c r="D35" t="s">
-        <v>141</v>
+        <v>279</v>
       </c>
       <c r="E35" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="F35" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>308</v>
+        <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C36" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D36" t="s">
         <v>141</v>
       </c>
       <c r="E36" t="s">
-        <v>311</v>
+        <v>143</v>
       </c>
       <c r="F36" t="s">
-        <v>143</v>
+        <v>312</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>313</v>
+        <v>15</v>
       </c>
       <c r="B37" t="s">
         <v>314</v>
       </c>
       <c r="C37" t="s">
-        <v>254</v>
+        <v>315</v>
       </c>
       <c r="D37" t="s">
         <v>141</v>
       </c>
       <c r="E37" t="s">
-        <v>315</v>
+        <v>143</v>
       </c>
       <c r="F37" t="s">
+        <v>143</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>317</v>
+      </c>
+      <c r="B38" t="s">
         <v>318</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" t="s">
         <v>319</v>
       </c>
-      <c r="C38" t="s">
+      <c r="F38" t="s">
         <v>320</v>
       </c>
-      <c r="D38" t="s">
-        <v>141</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="H38" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="F38" t="s">
-        <v>322</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>322</v>
+      </c>
+      <c r="B39" t="s">
+        <v>323</v>
+      </c>
+      <c r="C39" t="s">
         <v>324</v>
       </c>
-      <c r="B39" t="s">
+      <c r="D39" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" t="s">
+        <v>169</v>
+      </c>
+      <c r="F39" t="s">
         <v>325</v>
       </c>
-      <c r="C39" t="s">
+      <c r="H39" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="D39" t="s">
-        <v>269</v>
-      </c>
-      <c r="E39" t="s">
-        <v>327</v>
-      </c>
-      <c r="F39" t="s">
-        <v>328</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>327</v>
+      </c>
+      <c r="B40" t="s">
+        <v>328</v>
+      </c>
+      <c r="C40" t="s">
+        <v>329</v>
+      </c>
+      <c r="D40" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40" t="s">
         <v>330</v>
       </c>
-      <c r="B40" t="s">
+      <c r="F40" t="s">
+        <v>143</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="C40" t="s">
-        <v>332</v>
-      </c>
-      <c r="D40" t="s">
-        <v>141</v>
-      </c>
-      <c r="E40" t="s">
-        <v>333</v>
-      </c>
-      <c r="F40" t="s">
-        <v>334</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>332</v>
+      </c>
+      <c r="B41" t="s">
+        <v>333</v>
+      </c>
+      <c r="C41" t="s">
+        <v>264</v>
+      </c>
+      <c r="D41" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" t="s">
+        <v>334</v>
+      </c>
+      <c r="F41" t="s">
+        <v>335</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="B41" t="s">
-        <v>337</v>
-      </c>
-      <c r="C41" t="s">
-        <v>140</v>
-      </c>
-      <c r="D41" t="s">
-        <v>141</v>
-      </c>
-      <c r="E41" t="s">
-        <v>338</v>
-      </c>
-      <c r="F41" t="s">
-        <v>339</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>337</v>
+      </c>
+      <c r="B42" t="s">
+        <v>338</v>
+      </c>
+      <c r="C42" t="s">
+        <v>339</v>
+      </c>
+      <c r="D42" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" t="s">
+        <v>340</v>
+      </c>
+      <c r="F42" t="s">
         <v>341</v>
       </c>
-      <c r="B42" t="s">
+      <c r="H42" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="C42" t="s">
-        <v>140</v>
-      </c>
-      <c r="D42" t="s">
-        <v>141</v>
-      </c>
-      <c r="E42" t="s">
-        <v>343</v>
-      </c>
-      <c r="F42" t="s">
-        <v>344</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>343</v>
+      </c>
+      <c r="B43" t="s">
+        <v>344</v>
+      </c>
+      <c r="C43" t="s">
+        <v>345</v>
+      </c>
+      <c r="D43" t="s">
+        <v>279</v>
+      </c>
+      <c r="E43" t="s">
         <v>346</v>
       </c>
-      <c r="B43" t="s">
+      <c r="F43" t="s">
         <v>347</v>
       </c>
-      <c r="C43" t="s">
+      <c r="H43" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="D43" t="s">
-        <v>141</v>
-      </c>
-      <c r="E43" t="s">
-        <v>349</v>
-      </c>
-      <c r="F43" t="s">
-        <v>350</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>349</v>
+      </c>
+      <c r="B44" t="s">
+        <v>350</v>
+      </c>
+      <c r="C44" t="s">
+        <v>163</v>
+      </c>
+      <c r="D44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E44" t="s">
+        <v>351</v>
+      </c>
+      <c r="F44" t="s">
         <v>352</v>
       </c>
-      <c r="B44" t="s">
+      <c r="H44" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="C44" t="s">
-        <v>181</v>
-      </c>
-      <c r="D44" t="s">
-        <v>141</v>
-      </c>
-      <c r="E44" t="s">
-        <v>354</v>
-      </c>
-      <c r="F44" t="s">
-        <v>355</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>354</v>
+      </c>
+      <c r="B45" t="s">
+        <v>355</v>
+      </c>
+      <c r="C45" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45" t="s">
+        <v>141</v>
+      </c>
+      <c r="E45" t="s">
+        <v>356</v>
+      </c>
+      <c r="F45" t="s">
         <v>357</v>
       </c>
-      <c r="B45" t="s">
+      <c r="H45" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="C45" t="s">
-        <v>254</v>
-      </c>
-      <c r="D45" t="s">
-        <v>141</v>
-      </c>
-      <c r="E45" t="s">
-        <v>359</v>
-      </c>
-      <c r="F45" t="s">
-        <v>360</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>359</v>
+      </c>
+      <c r="B46" t="s">
+        <v>360</v>
+      </c>
+      <c r="C46" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" t="s">
+        <v>361</v>
+      </c>
+      <c r="F46" t="s">
         <v>362</v>
       </c>
-      <c r="B46" t="s">
+      <c r="H46" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="C46" t="s">
-        <v>364</v>
-      </c>
-      <c r="D46" t="s">
-        <v>141</v>
-      </c>
-      <c r="E46" t="s">
-        <v>365</v>
-      </c>
-      <c r="F46" t="s">
-        <v>194</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>364</v>
+      </c>
+      <c r="B47" t="s">
+        <v>365</v>
+      </c>
+      <c r="C47" t="s">
+        <v>366</v>
+      </c>
+      <c r="D47" t="s">
+        <v>141</v>
+      </c>
+      <c r="E47" t="s">
         <v>367</v>
       </c>
-      <c r="B47" t="s">
+      <c r="F47" t="s">
         <v>368</v>
       </c>
-      <c r="C47" t="s">
+      <c r="H47" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="D47" t="s">
-        <v>141</v>
-      </c>
-      <c r="E47" t="s">
-        <v>370</v>
-      </c>
-      <c r="F47" t="s">
-        <v>371</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>370</v>
+      </c>
+      <c r="B48" t="s">
+        <v>371</v>
+      </c>
+      <c r="C48" t="s">
+        <v>186</v>
+      </c>
+      <c r="D48" t="s">
+        <v>141</v>
+      </c>
+      <c r="E48" t="s">
+        <v>372</v>
+      </c>
+      <c r="F48" t="s">
         <v>373</v>
       </c>
-      <c r="B48" t="s">
+      <c r="H48" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="C48" t="s">
-        <v>375</v>
-      </c>
-      <c r="D48" t="s">
-        <v>260</v>
-      </c>
-      <c r="E48" t="s">
-        <v>376</v>
-      </c>
-      <c r="F48" t="s">
-        <v>377</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>375</v>
+      </c>
+      <c r="B49" t="s">
+        <v>376</v>
+      </c>
+      <c r="C49" t="s">
+        <v>264</v>
+      </c>
+      <c r="D49" t="s">
+        <v>141</v>
+      </c>
+      <c r="E49" t="s">
+        <v>377</v>
+      </c>
+      <c r="F49" t="s">
+        <v>378</v>
+      </c>
+      <c r="H49" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="B49" t="s">
-        <v>380</v>
-      </c>
-      <c r="C49" t="s">
-        <v>381</v>
-      </c>
-      <c r="D49" t="s">
-        <v>141</v>
-      </c>
-      <c r="E49" t="s">
-        <v>382</v>
-      </c>
-      <c r="F49" t="s">
-        <v>143</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>380</v>
+      </c>
+      <c r="B50" t="s">
+        <v>381</v>
+      </c>
+      <c r="C50" t="s">
+        <v>382</v>
+      </c>
+      <c r="D50" t="s">
+        <v>141</v>
+      </c>
+      <c r="E50" t="s">
+        <v>383</v>
+      </c>
+      <c r="F50" t="s">
+        <v>199</v>
+      </c>
+      <c r="H50" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="B50" t="s">
-        <v>385</v>
-      </c>
-      <c r="C50" t="s">
-        <v>386</v>
-      </c>
-      <c r="D50" t="s">
-        <v>141</v>
-      </c>
-      <c r="E50" t="s">
-        <v>387</v>
-      </c>
-      <c r="F50" t="s">
-        <v>143</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>385</v>
+      </c>
+      <c r="B51" t="s">
+        <v>386</v>
+      </c>
+      <c r="C51" t="s">
+        <v>387</v>
+      </c>
+      <c r="D51" t="s">
+        <v>141</v>
+      </c>
+      <c r="E51" t="s">
+        <v>388</v>
+      </c>
+      <c r="F51" t="s">
         <v>389</v>
       </c>
-      <c r="B51" t="s">
+      <c r="H51" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="C51" t="s">
-        <v>140</v>
-      </c>
-      <c r="D51" t="s">
-        <v>141</v>
-      </c>
-      <c r="E51" t="s">
-        <v>391</v>
-      </c>
-      <c r="F51" t="s">
-        <v>392</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>391</v>
+      </c>
+      <c r="B52" t="s">
+        <v>392</v>
+      </c>
+      <c r="C52" t="s">
+        <v>393</v>
+      </c>
+      <c r="D52" t="s">
+        <v>270</v>
+      </c>
+      <c r="E52" t="s">
         <v>394</v>
       </c>
-      <c r="B52" t="s">
+      <c r="F52" t="s">
         <v>395</v>
       </c>
-      <c r="C52" t="s">
+      <c r="H52" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="D52" t="s">
-        <v>141</v>
-      </c>
-      <c r="E52" t="s">
-        <v>397</v>
-      </c>
-      <c r="F52" t="s">
-        <v>398</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>397</v>
+      </c>
+      <c r="B53" t="s">
+        <v>398</v>
+      </c>
+      <c r="C53" t="s">
+        <v>399</v>
+      </c>
+      <c r="D53" t="s">
+        <v>141</v>
+      </c>
+      <c r="E53" t="s">
         <v>400</v>
       </c>
-      <c r="B53" t="s">
+      <c r="F53" t="s">
+        <v>143</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="C53" t="s">
-        <v>402</v>
-      </c>
-      <c r="D53" t="s">
-        <v>141</v>
-      </c>
-      <c r="E53" t="s">
-        <v>403</v>
-      </c>
-      <c r="F53" t="s">
-        <v>404</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B54" t="s">
+        <v>403</v>
+      </c>
+      <c r="C54" t="s">
+        <v>404</v>
+      </c>
+      <c r="D54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E54" t="s">
+        <v>405</v>
+      </c>
+      <c r="F54" t="s">
+        <v>143</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="C54" t="s">
-        <v>332</v>
-      </c>
-      <c r="D54" t="s">
-        <v>141</v>
-      </c>
-      <c r="E54" t="s">
-        <v>391</v>
-      </c>
-      <c r="F54" t="s">
-        <v>407</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>407</v>
+      </c>
+      <c r="B55" t="s">
+        <v>408</v>
+      </c>
+      <c r="C55" t="s">
+        <v>140</v>
+      </c>
+      <c r="D55" t="s">
+        <v>141</v>
+      </c>
+      <c r="E55" t="s">
         <v>409</v>
       </c>
-      <c r="B55" t="s">
+      <c r="F55" t="s">
         <v>410</v>
       </c>
-      <c r="C55" t="s">
+      <c r="H55" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="D55" t="s">
-        <v>141</v>
-      </c>
-      <c r="E55" t="s">
-        <v>412</v>
-      </c>
-      <c r="F55" t="s">
-        <v>413</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>412</v>
+      </c>
+      <c r="B56" t="s">
+        <v>413</v>
+      </c>
+      <c r="C56" t="s">
+        <v>414</v>
+      </c>
+      <c r="D56" t="s">
+        <v>141</v>
+      </c>
+      <c r="E56" t="s">
         <v>415</v>
       </c>
-      <c r="B56" t="s">
+      <c r="F56" t="s">
         <v>416</v>
       </c>
-      <c r="C56" t="s">
-        <v>181</v>
-      </c>
-      <c r="D56" t="s">
-        <v>141</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="H56" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="F56" t="s">
-        <v>418</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>418</v>
+      </c>
+      <c r="B57" t="s">
+        <v>419</v>
+      </c>
+      <c r="C57" t="s">
         <v>420</v>
       </c>
-      <c r="B57" t="s">
+      <c r="D57" t="s">
+        <v>141</v>
+      </c>
+      <c r="E57" t="s">
         <v>421</v>
       </c>
-      <c r="C57" t="s">
+      <c r="F57" t="s">
         <v>422</v>
       </c>
-      <c r="D57" t="s">
-        <v>141</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="H57" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="F57" t="s">
-        <v>424</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>418</v>
+      </c>
+      <c r="B58" t="s">
+        <v>424</v>
+      </c>
+      <c r="C58" t="s">
+        <v>163</v>
+      </c>
+      <c r="D58" t="s">
+        <v>141</v>
+      </c>
+      <c r="E58" t="s">
+        <v>409</v>
+      </c>
+      <c r="F58" t="s">
+        <v>425</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="B58" t="s">
-        <v>427</v>
-      </c>
-      <c r="C58" t="s">
-        <v>428</v>
-      </c>
-      <c r="D58" t="s">
-        <v>141</v>
-      </c>
-      <c r="E58" t="s">
-        <v>429</v>
-      </c>
-      <c r="F58" t="s">
-        <v>430</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>427</v>
+      </c>
+      <c r="B59" t="s">
+        <v>428</v>
+      </c>
+      <c r="C59" t="s">
+        <v>429</v>
+      </c>
+      <c r="D59" t="s">
+        <v>141</v>
+      </c>
+      <c r="E59" t="s">
+        <v>430</v>
+      </c>
+      <c r="F59" t="s">
+        <v>431</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="B59" t="s">
-        <v>433</v>
-      </c>
-      <c r="C59" t="s">
-        <v>140</v>
-      </c>
-      <c r="D59" t="s">
-        <v>141</v>
-      </c>
-      <c r="E59" t="s">
-        <v>434</v>
-      </c>
-      <c r="F59" t="s">
-        <v>435</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>433</v>
+      </c>
+      <c r="B60" t="s">
+        <v>434</v>
+      </c>
+      <c r="C60" t="s">
+        <v>186</v>
+      </c>
+      <c r="D60" t="s">
+        <v>141</v>
+      </c>
+      <c r="E60" t="s">
+        <v>435</v>
+      </c>
+      <c r="F60" t="s">
+        <v>436</v>
+      </c>
+      <c r="H60" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="B60" t="s">
-        <v>438</v>
-      </c>
-      <c r="C60" t="s">
-        <v>439</v>
-      </c>
-      <c r="D60" t="s">
-        <v>141</v>
-      </c>
-      <c r="E60" t="s">
-        <v>440</v>
-      </c>
-      <c r="F60" t="s">
-        <v>218</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>438</v>
+      </c>
+      <c r="B61" t="s">
+        <v>439</v>
+      </c>
+      <c r="C61" t="s">
+        <v>440</v>
+      </c>
+      <c r="D61" t="s">
+        <v>141</v>
+      </c>
+      <c r="E61" t="s">
+        <v>441</v>
+      </c>
+      <c r="F61" t="s">
         <v>442</v>
       </c>
-      <c r="B61" t="s">
+      <c r="H61" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="C61" t="s">
-        <v>444</v>
-      </c>
-      <c r="D61" t="s">
-        <v>141</v>
-      </c>
-      <c r="E61" t="s">
-        <v>445</v>
-      </c>
-      <c r="F61" t="s">
-        <v>446</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>444</v>
+      </c>
+      <c r="B62" t="s">
+        <v>445</v>
+      </c>
+      <c r="C62" t="s">
+        <v>446</v>
+      </c>
+      <c r="D62" t="s">
+        <v>141</v>
+      </c>
+      <c r="E62" t="s">
+        <v>447</v>
+      </c>
+      <c r="F62" t="s">
         <v>448</v>
       </c>
-      <c r="B62" t="s">
+      <c r="H62" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="C62" t="s">
-        <v>140</v>
-      </c>
-      <c r="D62" t="s">
-        <v>141</v>
-      </c>
-      <c r="E62" t="s">
-        <v>450</v>
-      </c>
-      <c r="F62" t="s">
-        <v>451</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>450</v>
+      </c>
+      <c r="B63" t="s">
+        <v>451</v>
+      </c>
+      <c r="C63" t="s">
+        <v>140</v>
+      </c>
+      <c r="D63" t="s">
+        <v>141</v>
+      </c>
+      <c r="E63" t="s">
+        <v>452</v>
+      </c>
+      <c r="F63" t="s">
         <v>453</v>
       </c>
-      <c r="B63" t="s">
+      <c r="H63" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="C63" t="s">
-        <v>187</v>
-      </c>
-      <c r="D63" t="s">
-        <v>141</v>
-      </c>
-      <c r="E63" t="s">
-        <v>455</v>
-      </c>
-      <c r="F63" t="s">
-        <v>456</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>455</v>
+      </c>
+      <c r="B64" t="s">
+        <v>456</v>
+      </c>
+      <c r="C64" t="s">
+        <v>457</v>
+      </c>
+      <c r="D64" t="s">
+        <v>141</v>
+      </c>
+      <c r="E64" t="s">
         <v>458</v>
       </c>
-      <c r="B64" t="s">
+      <c r="F64" t="s">
+        <v>223</v>
+      </c>
+      <c r="H64" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="C64" t="s">
-        <v>460</v>
-      </c>
-      <c r="D64" t="s">
-        <v>141</v>
-      </c>
-      <c r="E64" t="s">
-        <v>461</v>
-      </c>
-      <c r="F64" t="s">
-        <v>462</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>460</v>
+      </c>
+      <c r="B65" t="s">
+        <v>461</v>
+      </c>
+      <c r="C65" t="s">
+        <v>462</v>
+      </c>
+      <c r="D65" t="s">
+        <v>141</v>
+      </c>
+      <c r="E65" t="s">
+        <v>463</v>
+      </c>
+      <c r="F65" t="s">
         <v>464</v>
       </c>
-      <c r="B65" t="s">
+      <c r="H65" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="C65" t="s">
-        <v>140</v>
-      </c>
-      <c r="D65" t="s">
-        <v>269</v>
-      </c>
-      <c r="E65" t="s">
-        <v>466</v>
-      </c>
-      <c r="F65" t="s">
-        <v>467</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>466</v>
+      </c>
+      <c r="B66" t="s">
+        <v>467</v>
+      </c>
+      <c r="C66" t="s">
+        <v>140</v>
+      </c>
+      <c r="D66" t="s">
+        <v>141</v>
+      </c>
+      <c r="E66" t="s">
+        <v>468</v>
+      </c>
+      <c r="F66" t="s">
         <v>469</v>
       </c>
-      <c r="B66" t="s">
+      <c r="H66" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="C66" t="s">
-        <v>254</v>
-      </c>
-      <c r="D66" t="s">
-        <v>141</v>
-      </c>
-      <c r="E66" t="s">
-        <v>471</v>
-      </c>
-      <c r="F66" t="s">
-        <v>472</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>471</v>
+      </c>
+      <c r="B67" t="s">
+        <v>472</v>
+      </c>
+      <c r="C67" t="s">
+        <v>192</v>
+      </c>
+      <c r="D67" t="s">
+        <v>141</v>
+      </c>
+      <c r="E67" t="s">
+        <v>473</v>
+      </c>
+      <c r="F67" t="s">
         <v>474</v>
       </c>
-      <c r="B67" t="s">
-        <v>470</v>
-      </c>
-      <c r="C67" t="s">
-        <v>254</v>
-      </c>
-      <c r="D67" t="s">
-        <v>141</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="H67" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="F67" t="s">
-        <v>143</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>476</v>
+      </c>
+      <c r="B68" t="s">
         <v>477</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>478</v>
-      </c>
-      <c r="C68" t="s">
-        <v>305</v>
       </c>
       <c r="D68" t="s">
         <v>141</v>
@@ -4888,76 +4978,76 @@
         <v>479</v>
       </c>
       <c r="F68" t="s">
-        <v>143</v>
+        <v>480</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B69" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C69" t="s">
-        <v>305</v>
+        <v>140</v>
       </c>
       <c r="D69" t="s">
-        <v>141</v>
+        <v>279</v>
       </c>
       <c r="E69" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F69" t="s">
-        <v>143</v>
+        <v>485</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B70" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C70" t="s">
-        <v>486</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
         <v>141</v>
       </c>
       <c r="E70" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F70" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B71" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C71" t="s">
-        <v>492</v>
+        <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>269</v>
+        <v>141</v>
       </c>
       <c r="E71" t="s">
+        <v>493</v>
+      </c>
+      <c r="F71" t="s">
         <v>143</v>
-      </c>
-      <c r="F71" t="s">
-        <v>493</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>494</v>
@@ -4971,7 +5061,7 @@
         <v>496</v>
       </c>
       <c r="C72" t="s">
-        <v>381</v>
+        <v>324</v>
       </c>
       <c r="D72" t="s">
         <v>141</v>
@@ -4980,165 +5070,165 @@
         <v>497</v>
       </c>
       <c r="F72" t="s">
+        <v>143</v>
+      </c>
+      <c r="H72" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B73" t="s">
         <v>496</v>
       </c>
       <c r="C73" t="s">
-        <v>187</v>
+        <v>324</v>
       </c>
       <c r="D73" t="s">
         <v>141</v>
       </c>
       <c r="E73" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F73" t="s">
-        <v>498</v>
+        <v>143</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B74" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C74" t="s">
-        <v>140</v>
+        <v>504</v>
       </c>
       <c r="D74" t="s">
-        <v>269</v>
+        <v>141</v>
       </c>
       <c r="E74" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F74" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B75" t="s">
-        <v>157</v>
+        <v>509</v>
       </c>
       <c r="C75" t="s">
-        <v>158</v>
+        <v>510</v>
       </c>
       <c r="D75" t="s">
-        <v>141</v>
+        <v>279</v>
       </c>
       <c r="E75" t="s">
-        <v>265</v>
+        <v>143</v>
       </c>
       <c r="F75" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B76" t="s">
-        <v>191</v>
+        <v>514</v>
       </c>
       <c r="C76" t="s">
-        <v>192</v>
+        <v>399</v>
       </c>
       <c r="D76" t="s">
         <v>141</v>
       </c>
       <c r="E76" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="F76" t="s">
-        <v>194</v>
+        <v>516</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B77" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C77" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="D77" t="s">
         <v>141</v>
       </c>
       <c r="E77" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F77" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B78" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C78" t="s">
-        <v>519</v>
+        <v>140</v>
       </c>
       <c r="D78" t="s">
-        <v>141</v>
+        <v>279</v>
       </c>
       <c r="E78" t="s">
-        <v>143</v>
+        <v>521</v>
       </c>
       <c r="F78" t="s">
-        <v>143</v>
+        <v>522</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B79" t="s">
-        <v>522</v>
+        <v>157</v>
       </c>
       <c r="C79" t="s">
-        <v>523</v>
+        <v>158</v>
       </c>
       <c r="D79" t="s">
         <v>141</v>
       </c>
       <c r="E79" t="s">
-        <v>524</v>
+        <v>275</v>
       </c>
       <c r="F79" t="s">
         <v>525</v>
@@ -5152,42 +5242,42 @@
         <v>527</v>
       </c>
       <c r="B80" t="s">
+        <v>196</v>
+      </c>
+      <c r="C80" t="s">
+        <v>197</v>
+      </c>
+      <c r="D80" t="s">
+        <v>141</v>
+      </c>
+      <c r="E80" t="s">
         <v>528</v>
       </c>
-      <c r="C80" t="s">
+      <c r="F80" t="s">
+        <v>199</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="D80" t="s">
-        <v>141</v>
-      </c>
-      <c r="E80" t="s">
-        <v>530</v>
-      </c>
-      <c r="F80" t="s">
-        <v>531</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>530</v>
+      </c>
+      <c r="B81" t="s">
+        <v>531</v>
+      </c>
+      <c r="C81" t="s">
+        <v>140</v>
+      </c>
+      <c r="D81" t="s">
+        <v>141</v>
+      </c>
+      <c r="E81" t="s">
+        <v>532</v>
+      </c>
+      <c r="F81" t="s">
         <v>533</v>
-      </c>
-      <c r="B81" t="s">
-        <v>253</v>
-      </c>
-      <c r="C81" t="s">
-        <v>254</v>
-      </c>
-      <c r="D81" t="s">
-        <v>141</v>
-      </c>
-      <c r="E81" t="s">
-        <v>397</v>
-      </c>
-      <c r="F81" t="s">
-        <v>256</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>534</v>
@@ -5204,27 +5294,27 @@
         <v>537</v>
       </c>
       <c r="D82" t="s">
-        <v>199</v>
+        <v>141</v>
       </c>
       <c r="E82" t="s">
         <v>143</v>
       </c>
       <c r="F82" t="s">
+        <v>143</v>
+      </c>
+      <c r="H82" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>539</v>
+      </c>
+      <c r="B83" t="s">
         <v>540</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>541</v>
-      </c>
-      <c r="C83" t="s">
-        <v>348</v>
       </c>
       <c r="D83" t="s">
         <v>141</v>
@@ -5244,42 +5334,42 @@
         <v>545</v>
       </c>
       <c r="B84" t="s">
-        <v>410</v>
+        <v>546</v>
       </c>
       <c r="C84" t="s">
-        <v>411</v>
+        <v>547</v>
       </c>
       <c r="D84" t="s">
         <v>141</v>
       </c>
       <c r="E84" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F84" t="s">
-        <v>413</v>
+        <v>549</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B85" t="s">
-        <v>549</v>
+        <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>175</v>
+        <v>264</v>
       </c>
       <c r="D85" t="s">
         <v>141</v>
       </c>
       <c r="E85" t="s">
-        <v>550</v>
+        <v>415</v>
       </c>
       <c r="F85" t="s">
-        <v>551</v>
+        <v>266</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>552</v>
@@ -5290,111 +5380,111 @@
         <v>553</v>
       </c>
       <c r="B86" t="s">
-        <v>157</v>
+        <v>554</v>
       </c>
       <c r="C86" t="s">
-        <v>158</v>
+        <v>555</v>
       </c>
       <c r="D86" t="s">
-        <v>141</v>
+        <v>204</v>
       </c>
       <c r="E86" t="s">
-        <v>265</v>
+        <v>143</v>
       </c>
       <c r="F86" t="s">
-        <v>160</v>
+        <v>556</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s">
-        <v>157</v>
+        <v>559</v>
       </c>
       <c r="C87" t="s">
-        <v>158</v>
+        <v>366</v>
       </c>
       <c r="D87" t="s">
         <v>141</v>
       </c>
       <c r="E87" t="s">
-        <v>265</v>
+        <v>560</v>
       </c>
       <c r="F87" t="s">
-        <v>160</v>
+        <v>561</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B88" t="s">
-        <v>558</v>
+        <v>428</v>
       </c>
       <c r="C88" t="s">
-        <v>559</v>
+        <v>429</v>
       </c>
       <c r="D88" t="s">
-        <v>260</v>
+        <v>141</v>
       </c>
       <c r="E88" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F88" t="s">
-        <v>561</v>
+        <v>431</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B89" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C89" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D89" t="s">
         <v>141</v>
       </c>
       <c r="E89" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="F89" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B90" t="s">
-        <v>569</v>
+        <v>157</v>
       </c>
       <c r="C90" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D90" t="s">
         <v>141</v>
       </c>
       <c r="E90" t="s">
-        <v>570</v>
+        <v>275</v>
       </c>
       <c r="F90" t="s">
-        <v>571</v>
+        <v>160</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>572</v>
@@ -5405,145 +5495,145 @@
         <v>573</v>
       </c>
       <c r="B91" t="s">
+        <v>157</v>
+      </c>
+      <c r="C91" t="s">
+        <v>158</v>
+      </c>
+      <c r="D91" t="s">
+        <v>141</v>
+      </c>
+      <c r="E91" t="s">
+        <v>275</v>
+      </c>
+      <c r="F91" t="s">
+        <v>160</v>
+      </c>
+      <c r="H91" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="C91" t="s">
-        <v>181</v>
-      </c>
-      <c r="D91" t="s">
-        <v>141</v>
-      </c>
-      <c r="E91" t="s">
-        <v>475</v>
-      </c>
-      <c r="F91" t="s">
-        <v>575</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>575</v>
+      </c>
+      <c r="B92" t="s">
+        <v>576</v>
+      </c>
+      <c r="C92" t="s">
         <v>577</v>
       </c>
-      <c r="B92" t="s">
+      <c r="D92" t="s">
+        <v>270</v>
+      </c>
+      <c r="E92" t="s">
         <v>578</v>
       </c>
-      <c r="C92" t="s">
+      <c r="F92" t="s">
         <v>579</v>
       </c>
-      <c r="D92" t="s">
-        <v>141</v>
-      </c>
-      <c r="E92" t="s">
-        <v>445</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="H92" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B93" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C93" t="s">
-        <v>582</v>
+        <v>192</v>
       </c>
       <c r="D93" t="s">
         <v>141</v>
       </c>
       <c r="E93" t="s">
-        <v>445</v>
+        <v>583</v>
       </c>
       <c r="F93" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B94" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C94" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="D94" t="s">
-        <v>260</v>
+        <v>141</v>
       </c>
       <c r="E94" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F94" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B95" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C95" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D95" t="s">
         <v>141</v>
       </c>
       <c r="E95" t="s">
-        <v>591</v>
+        <v>493</v>
       </c>
       <c r="F95" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B96" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C96" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D96" t="s">
         <v>141</v>
       </c>
       <c r="E96" t="s">
-        <v>597</v>
+        <v>463</v>
       </c>
       <c r="F96" t="s">
-        <v>284</v>
+        <v>598</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B97" t="s">
-        <v>253</v>
+        <v>596</v>
       </c>
       <c r="C97" t="s">
         <v>600</v>
@@ -5552,33 +5642,33 @@
         <v>141</v>
       </c>
       <c r="E97" t="s">
+        <v>463</v>
+      </c>
+      <c r="F97" t="s">
+        <v>598</v>
+      </c>
+      <c r="H97" s="2" t="s">
         <v>601</v>
-      </c>
-      <c r="F97" t="s">
-        <v>256</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>602</v>
+      </c>
+      <c r="B98" t="s">
         <v>603</v>
-      </c>
-      <c r="B98" t="s">
-        <v>604</v>
       </c>
       <c r="C98" t="s">
         <v>140</v>
       </c>
       <c r="D98" t="s">
-        <v>141</v>
+        <v>270</v>
       </c>
       <c r="E98" t="s">
+        <v>604</v>
+      </c>
+      <c r="F98" t="s">
         <v>605</v>
-      </c>
-      <c r="F98" t="s">
-        <v>344</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>606</v>
@@ -5592,7 +5682,7 @@
         <v>608</v>
       </c>
       <c r="C99" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D99" t="s">
         <v>141</v>
@@ -5624,168 +5714,168 @@
         <v>615</v>
       </c>
       <c r="F100" t="s">
+        <v>300</v>
+      </c>
+      <c r="H100" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>617</v>
+      </c>
+      <c r="B101" t="s">
+        <v>263</v>
+      </c>
+      <c r="C101" t="s">
+        <v>283</v>
+      </c>
+      <c r="D101" t="s">
+        <v>141</v>
+      </c>
+      <c r="E101" t="s">
         <v>618</v>
       </c>
-      <c r="B101" t="s">
+      <c r="F101" t="s">
+        <v>266</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>619</v>
-      </c>
-      <c r="C101" t="s">
-        <v>620</v>
-      </c>
-      <c r="D101" t="s">
-        <v>141</v>
-      </c>
-      <c r="E101" t="s">
-        <v>621</v>
-      </c>
-      <c r="F101" t="s">
-        <v>622</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B102" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C102" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="D102" t="s">
         <v>141</v>
       </c>
       <c r="E102" t="s">
-        <v>627</v>
+        <v>143</v>
       </c>
       <c r="F102" t="s">
-        <v>628</v>
+        <v>143</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="B103" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="C103" t="s">
-        <v>632</v>
+        <v>140</v>
       </c>
       <c r="D103" t="s">
         <v>141</v>
       </c>
       <c r="E103" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="F103" t="s">
-        <v>634</v>
+        <v>362</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="B104" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="C104" t="s">
-        <v>288</v>
+        <v>28</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>141</v>
       </c>
       <c r="E104" t="s">
-        <v>143</v>
+        <v>630</v>
       </c>
       <c r="F104" t="s">
-        <v>171</v>
+        <v>631</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="B105" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C105" t="s">
-        <v>153</v>
+        <v>635</v>
       </c>
       <c r="D105" t="s">
         <v>141</v>
       </c>
       <c r="E105" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="F105" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>639</v>
+      </c>
+      <c r="B106" t="s">
+        <v>640</v>
+      </c>
+      <c r="C106" t="s">
+        <v>641</v>
+      </c>
+      <c r="D106" t="s">
+        <v>141</v>
+      </c>
+      <c r="E106" t="s">
+        <v>642</v>
+      </c>
+      <c r="F106" t="s">
+        <v>643</v>
+      </c>
+      <c r="H106" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="B106" t="s">
-        <v>470</v>
-      </c>
-      <c r="C106" t="s">
-        <v>254</v>
-      </c>
-      <c r="D106" t="s">
-        <v>141</v>
-      </c>
-      <c r="E106" t="s">
-        <v>255</v>
-      </c>
-      <c r="F106" t="s">
-        <v>645</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>645</v>
+      </c>
+      <c r="B107" t="s">
+        <v>646</v>
+      </c>
+      <c r="C107" t="s">
         <v>647</v>
       </c>
-      <c r="B107" t="s">
+      <c r="D107" t="s">
+        <v>141</v>
+      </c>
+      <c r="E107" t="s">
         <v>648</v>
       </c>
-      <c r="C107" t="s">
-        <v>140</v>
-      </c>
-      <c r="D107" t="s">
-        <v>260</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>649</v>
-      </c>
-      <c r="F107" t="s">
-        <v>451</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>650</v>
@@ -5793,91 +5883,91 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B108" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="C108" t="s">
-        <v>153</v>
+        <v>653</v>
       </c>
       <c r="D108" t="s">
         <v>141</v>
       </c>
       <c r="E108" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="F108" t="s">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B109" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C109" t="s">
-        <v>254</v>
+        <v>304</v>
       </c>
       <c r="D109" t="s">
-        <v>141</v>
+        <v>279</v>
       </c>
       <c r="E109" t="s">
-        <v>655</v>
+        <v>143</v>
       </c>
       <c r="F109" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="B110" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C110" t="s">
-        <v>659</v>
+        <v>153</v>
       </c>
       <c r="D110" t="s">
-        <v>199</v>
+        <v>141</v>
       </c>
       <c r="E110" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F110" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B111" t="s">
-        <v>664</v>
+        <v>488</v>
       </c>
       <c r="C111" t="s">
-        <v>665</v>
+        <v>264</v>
       </c>
       <c r="D111" t="s">
-        <v>269</v>
+        <v>141</v>
       </c>
       <c r="E111" t="s">
+        <v>265</v>
+      </c>
+      <c r="F111" t="s">
         <v>666</v>
-      </c>
-      <c r="F111" t="s">
-        <v>322</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>667</v>
@@ -5888,88 +5978,88 @@
         <v>668</v>
       </c>
       <c r="B112" t="s">
-        <v>157</v>
+        <v>669</v>
       </c>
       <c r="C112" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="D112" t="s">
-        <v>141</v>
+        <v>270</v>
       </c>
       <c r="E112" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F112" t="s">
-        <v>160</v>
+        <v>469</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B113" t="s">
+        <v>661</v>
+      </c>
+      <c r="C113" t="s">
+        <v>153</v>
+      </c>
+      <c r="D113" t="s">
+        <v>141</v>
+      </c>
+      <c r="E113" t="s">
         <v>672</v>
       </c>
-      <c r="C113" t="s">
-        <v>140</v>
-      </c>
-      <c r="D113" t="s">
-        <v>141</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
+        <v>663</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="F113" t="s">
-        <v>674</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>674</v>
+      </c>
+      <c r="B114" t="s">
+        <v>675</v>
+      </c>
+      <c r="C114" t="s">
+        <v>264</v>
+      </c>
+      <c r="D114" t="s">
+        <v>141</v>
+      </c>
+      <c r="E114" t="s">
         <v>676</v>
       </c>
-      <c r="B114" t="s">
+      <c r="F114" t="s">
+        <v>143</v>
+      </c>
+      <c r="H114" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="C114" t="s">
-        <v>140</v>
-      </c>
-      <c r="D114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E114" t="s">
-        <v>678</v>
-      </c>
-      <c r="F114" t="s">
-        <v>679</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>678</v>
+      </c>
+      <c r="B115" t="s">
+        <v>679</v>
+      </c>
+      <c r="C115" t="s">
+        <v>680</v>
+      </c>
+      <c r="D115" t="s">
+        <v>204</v>
+      </c>
+      <c r="E115" t="s">
         <v>681</v>
       </c>
-      <c r="B115" t="s">
-        <v>625</v>
-      </c>
-      <c r="C115" t="s">
-        <v>626</v>
-      </c>
-      <c r="D115" t="s">
-        <v>260</v>
-      </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>682</v>
-      </c>
-      <c r="F115" t="s">
-        <v>628</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>683</v>
@@ -5980,42 +6070,42 @@
         <v>684</v>
       </c>
       <c r="B116" t="s">
-        <v>139</v>
+        <v>685</v>
       </c>
       <c r="C116" t="s">
-        <v>140</v>
+        <v>686</v>
       </c>
       <c r="D116" t="s">
-        <v>141</v>
+        <v>279</v>
       </c>
       <c r="E116" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="F116" t="s">
-        <v>143</v>
+        <v>341</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B117" t="s">
-        <v>688</v>
+        <v>157</v>
       </c>
       <c r="C117" t="s">
-        <v>254</v>
+        <v>158</v>
       </c>
       <c r="D117" t="s">
         <v>141</v>
       </c>
       <c r="E117" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F117" t="s">
-        <v>690</v>
+        <v>160</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>691</v>
@@ -6029,7 +6119,7 @@
         <v>693</v>
       </c>
       <c r="C118" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="D118" t="s">
         <v>141</v>
@@ -6049,7 +6139,7 @@
         <v>697</v>
       </c>
       <c r="B119" t="s">
-        <v>139</v>
+        <v>698</v>
       </c>
       <c r="C119" t="s">
         <v>140</v>
@@ -6058,217 +6148,217 @@
         <v>141</v>
       </c>
       <c r="E119" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F119" t="s">
-        <v>143</v>
+        <v>700</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B120" t="s">
-        <v>454</v>
+        <v>646</v>
       </c>
       <c r="C120" t="s">
-        <v>701</v>
+        <v>647</v>
       </c>
       <c r="D120" t="s">
-        <v>141</v>
+        <v>270</v>
       </c>
       <c r="E120" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="F120" t="s">
-        <v>143</v>
+        <v>649</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B121" t="s">
-        <v>152</v>
+        <v>706</v>
       </c>
       <c r="C121" t="s">
-        <v>153</v>
+        <v>707</v>
       </c>
       <c r="D121" t="s">
         <v>141</v>
       </c>
       <c r="E121" t="s">
-        <v>154</v>
+        <v>708</v>
       </c>
       <c r="F121" t="s">
-        <v>155</v>
+        <v>709</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="B122" t="s">
-        <v>688</v>
+        <v>139</v>
       </c>
       <c r="C122" t="s">
-        <v>707</v>
+        <v>140</v>
       </c>
       <c r="D122" t="s">
         <v>141</v>
       </c>
       <c r="E122" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="F122" t="s">
-        <v>690</v>
+        <v>143</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B123" t="s">
-        <v>470</v>
+        <v>715</v>
       </c>
       <c r="C123" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="D123" t="s">
         <v>141</v>
       </c>
       <c r="E123" t="s">
-        <v>255</v>
+        <v>716</v>
       </c>
       <c r="F123" t="s">
-        <v>543</v>
+        <v>717</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="B124" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="C124" t="s">
-        <v>714</v>
+        <v>264</v>
       </c>
       <c r="D124" t="s">
         <v>141</v>
       </c>
       <c r="E124" t="s">
-        <v>475</v>
+        <v>721</v>
       </c>
       <c r="F124" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="B125" t="s">
-        <v>718</v>
+        <v>139</v>
       </c>
       <c r="C125" t="s">
-        <v>719</v>
+        <v>140</v>
       </c>
       <c r="D125" t="s">
         <v>141</v>
       </c>
       <c r="E125" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="F125" t="s">
-        <v>721</v>
+        <v>143</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B126" t="s">
-        <v>608</v>
+        <v>472</v>
       </c>
       <c r="C126" t="s">
-        <v>28</v>
+        <v>707</v>
       </c>
       <c r="D126" t="s">
         <v>141</v>
       </c>
       <c r="E126" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="F126" t="s">
-        <v>610</v>
+        <v>143</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="B127" t="s">
-        <v>727</v>
+        <v>152</v>
       </c>
       <c r="C127" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="D127" t="s">
-        <v>269</v>
+        <v>141</v>
       </c>
       <c r="E127" t="s">
-        <v>728</v>
+        <v>154</v>
       </c>
       <c r="F127" t="s">
-        <v>729</v>
+        <v>155</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B128" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="C128" t="s">
-        <v>140</v>
+        <v>733</v>
       </c>
       <c r="D128" t="s">
         <v>141</v>
       </c>
       <c r="E128" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F128" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>735</v>
@@ -6279,91 +6369,252 @@
         <v>736</v>
       </c>
       <c r="B129" t="s">
-        <v>564</v>
+        <v>488</v>
       </c>
       <c r="C129" t="s">
-        <v>614</v>
+        <v>264</v>
       </c>
       <c r="D129" t="s">
         <v>141</v>
       </c>
       <c r="E129" t="s">
+        <v>265</v>
+      </c>
+      <c r="F129" t="s">
+        <v>561</v>
+      </c>
+      <c r="H129" s="2" t="s">
         <v>737</v>
-      </c>
-      <c r="F129" t="s">
-        <v>738</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>738</v>
+      </c>
+      <c r="B130" t="s">
+        <v>706</v>
+      </c>
+      <c r="C130" t="s">
+        <v>707</v>
+      </c>
+      <c r="D130" t="s">
+        <v>141</v>
+      </c>
+      <c r="E130" t="s">
+        <v>739</v>
+      </c>
+      <c r="F130" t="s">
         <v>740</v>
       </c>
-      <c r="B130" t="s">
+      <c r="H130" s="2" t="s">
         <v>741</v>
-      </c>
-      <c r="C130" t="s">
-        <v>140</v>
-      </c>
-      <c r="D130" t="s">
-        <v>141</v>
-      </c>
-      <c r="E130" t="s">
-        <v>742</v>
-      </c>
-      <c r="F130" t="s">
-        <v>743</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>742</v>
+      </c>
+      <c r="B131" t="s">
+        <v>743</v>
+      </c>
+      <c r="C131" t="s">
+        <v>744</v>
+      </c>
+      <c r="D131" t="s">
+        <v>141</v>
+      </c>
+      <c r="E131" t="s">
+        <v>493</v>
+      </c>
+      <c r="F131" t="s">
         <v>745</v>
       </c>
-      <c r="B131" t="s">
+      <c r="H131" s="2" t="s">
         <v>746</v>
-      </c>
-      <c r="C131" t="s">
-        <v>747</v>
-      </c>
-      <c r="D131" t="s">
-        <v>269</v>
-      </c>
-      <c r="E131" t="s">
-        <v>143</v>
-      </c>
-      <c r="F131" t="s">
-        <v>748</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>747</v>
+      </c>
+      <c r="B132" t="s">
+        <v>748</v>
+      </c>
+      <c r="C132" t="s">
+        <v>749</v>
+      </c>
+      <c r="D132" t="s">
+        <v>141</v>
+      </c>
+      <c r="E132" t="s">
         <v>750</v>
       </c>
-      <c r="B132" t="s">
+      <c r="F132" t="s">
         <v>751</v>
       </c>
-      <c r="C132" t="s">
-        <v>254</v>
-      </c>
-      <c r="D132" t="s">
-        <v>141</v>
-      </c>
-      <c r="E132" t="s">
+      <c r="H132" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="F132" t="s">
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>753</v>
       </c>
-      <c r="H132" s="2" t="s">
+      <c r="B133" t="s">
+        <v>629</v>
+      </c>
+      <c r="C133" t="s">
+        <v>28</v>
+      </c>
+      <c r="D133" t="s">
+        <v>141</v>
+      </c>
+      <c r="E133" t="s">
         <v>754</v>
+      </c>
+      <c r="F133" t="s">
+        <v>631</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>756</v>
+      </c>
+      <c r="B134" t="s">
+        <v>757</v>
+      </c>
+      <c r="C134" t="s">
+        <v>140</v>
+      </c>
+      <c r="D134" t="s">
+        <v>279</v>
+      </c>
+      <c r="E134" t="s">
+        <v>758</v>
+      </c>
+      <c r="F134" t="s">
+        <v>759</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>761</v>
+      </c>
+      <c r="B135" t="s">
+        <v>762</v>
+      </c>
+      <c r="C135" t="s">
+        <v>140</v>
+      </c>
+      <c r="D135" t="s">
+        <v>141</v>
+      </c>
+      <c r="E135" t="s">
+        <v>763</v>
+      </c>
+      <c r="F135" t="s">
+        <v>764</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>766</v>
+      </c>
+      <c r="B136" t="s">
+        <v>582</v>
+      </c>
+      <c r="C136" t="s">
+        <v>635</v>
+      </c>
+      <c r="D136" t="s">
+        <v>141</v>
+      </c>
+      <c r="E136" t="s">
+        <v>767</v>
+      </c>
+      <c r="F136" t="s">
+        <v>768</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>770</v>
+      </c>
+      <c r="B137" t="s">
+        <v>771</v>
+      </c>
+      <c r="C137" t="s">
+        <v>140</v>
+      </c>
+      <c r="D137" t="s">
+        <v>141</v>
+      </c>
+      <c r="E137" t="s">
+        <v>772</v>
+      </c>
+      <c r="F137" t="s">
+        <v>773</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>775</v>
+      </c>
+      <c r="B138" t="s">
+        <v>776</v>
+      </c>
+      <c r="C138" t="s">
+        <v>777</v>
+      </c>
+      <c r="D138" t="s">
+        <v>279</v>
+      </c>
+      <c r="E138" t="s">
+        <v>143</v>
+      </c>
+      <c r="F138" t="s">
+        <v>778</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>780</v>
+      </c>
+      <c r="B139" t="s">
+        <v>781</v>
+      </c>
+      <c r="C139" t="s">
+        <v>264</v>
+      </c>
+      <c r="D139" t="s">
+        <v>141</v>
+      </c>
+      <c r="E139" t="s">
+        <v>782</v>
+      </c>
+      <c r="F139" t="s">
+        <v>783</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>784</v>
       </c>
     </row>
   </sheetData>
@@ -6500,6 +6751,13 @@
     <hyperlink ref="H130" r:id="rId129"/>
     <hyperlink ref="H131" r:id="rId130"/>
     <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
